--- a/Tax_Legal_Finance_Events_Master_100_Organizations.xlsx
+++ b/Tax_Legal_Finance_Events_Master_100_Organizations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://m2kadvisors-my.sharepoint.com/personal/marketing_m2k_co_in/Documents/Documents/Expertly/expertly-portal-design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_B1DA68B389CEF466FE1A8817412D1E7D49742010" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88C7DB17-A4D7-451E-98BF-5568EA03790B}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_C5B5A3EC2318259281614454452D1E7D7979D0E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14A3E631-0DC0-4B03-AC37-5253E2C15E76}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,27 +16,14 @@
     <sheet name="Organizations" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Organizations!$A$1:$E$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Organizations!$A$1:$E$250</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="734">
   <si>
     <t>#</t>
   </si>
@@ -62,6 +49,9 @@
     <t>India</t>
   </si>
   <si>
+    <t>https://cpeicai.org/#events</t>
+  </si>
+  <si>
     <t>ICAI Direct Taxes Committee</t>
   </si>
   <si>
@@ -695,1143 +685,1098 @@
     <t>https://www.ifrs.org/news-and-events/events/</t>
   </si>
   <si>
-    <t>SASB</t>
+    <t>AGA</t>
+  </si>
+  <si>
+    <t>Government Finance</t>
+  </si>
+  <si>
+    <t>https://www.agacgfm.org/Events.aspx</t>
+  </si>
+  <si>
+    <t>NASBA</t>
+  </si>
+  <si>
+    <t>https://nasba.org/events/</t>
+  </si>
+  <si>
+    <t>IMA</t>
+  </si>
+  <si>
+    <t>Management Accounting</t>
+  </si>
+  <si>
+    <t>https://www.imanet.org/events</t>
+  </si>
+  <si>
+    <t>FMA</t>
+  </si>
+  <si>
+    <t>https://fma.org/events</t>
+  </si>
+  <si>
+    <t>Global Finance Conferences</t>
+  </si>
+  <si>
+    <t>https://globalfinanceconference.com/conference/</t>
+  </si>
+  <si>
+    <t>EAA</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>https://eaa-online.org/events/</t>
+  </si>
+  <si>
+    <t>EFMA</t>
+  </si>
+  <si>
+    <t>https://www.efmaefm.org/events/</t>
+  </si>
+  <si>
+    <t>IAAER</t>
+  </si>
+  <si>
+    <t>https://www.iaaer.org/events</t>
+  </si>
+  <si>
+    <t>ICV</t>
+  </si>
+  <si>
+    <t>Controlling</t>
+  </si>
+  <si>
+    <t>https://icv-controlling.com/en/events/</t>
+  </si>
+  <si>
+    <t>ACT</t>
+  </si>
+  <si>
+    <t>https://www.treasurers.org/events</t>
+  </si>
+  <si>
+    <t>EuroFinance</t>
+  </si>
+  <si>
+    <t>https://www.eurofinance.com/events</t>
+  </si>
+  <si>
+    <t>ABS Singapore</t>
+  </si>
+  <si>
+    <t>https://abs.org.sg/events</t>
+  </si>
+  <si>
+    <t>IAFEI</t>
+  </si>
+  <si>
+    <t>https://iafei.org/events</t>
+  </si>
+  <si>
+    <t>IBE</t>
+  </si>
+  <si>
+    <t>Ethics</t>
+  </si>
+  <si>
+    <t>https://www.ibe.org.uk/events.html</t>
+  </si>
+  <si>
+    <t>ECI</t>
+  </si>
+  <si>
+    <t>https://www.ethics.org/events/</t>
+  </si>
+  <si>
+    <t>NAEA</t>
+  </si>
+  <si>
+    <t>https://www.naea.org/events/</t>
+  </si>
+  <si>
+    <t>International Association of Insurance Supervisors (IAIS)</t>
+  </si>
+  <si>
+    <t>Insurance Regulation</t>
+  </si>
+  <si>
+    <t>https://www.iaisweb.org/events/</t>
+  </si>
+  <si>
+    <t>International Association of Financial Crimes Investigators (IAFCI)</t>
+  </si>
+  <si>
+    <t>Financial Crime</t>
+  </si>
+  <si>
+    <t>https://www.iafci.org/events</t>
+  </si>
+  <si>
+    <t>Association of Certified Anti-Money Laundering Specialists (ACAMS)</t>
+  </si>
+  <si>
+    <t>AML &amp; Compliance</t>
+  </si>
+  <si>
+    <t>https://www.acams.org/en/events</t>
+  </si>
+  <si>
+    <t>Association of Corporate Investigators (ACI)</t>
+  </si>
+  <si>
+    <t>Corporate Investigations</t>
+  </si>
+  <si>
+    <t>https://www.aci.org.uk/events</t>
+  </si>
+  <si>
+    <t>Institute of Certified Bookkeepers (ICB)</t>
+  </si>
+  <si>
+    <t>Bookkeeping</t>
+  </si>
+  <si>
+    <t>https://www.bookkeepers.org.uk/training-and-events</t>
+  </si>
+  <si>
+    <t>Association of International Certified Professional Accountants - UK</t>
+  </si>
+  <si>
+    <t>https://www.aicpa-cima.com/events</t>
+  </si>
+  <si>
+    <t>European Banking Federation (EBF)</t>
+  </si>
+  <si>
+    <t>https://www.ebf.eu/events/</t>
+  </si>
+  <si>
+    <t>European Association of Co-operative Banks (EACB)</t>
+  </si>
+  <si>
+    <t>https://www.eacb.coop/en/events.html</t>
+  </si>
+  <si>
+    <t>International Securities Lending Association (ISLA)</t>
+  </si>
+  <si>
+    <t>https://www.islaemea.org/events/</t>
+  </si>
+  <si>
+    <t>Association for Financial Markets in Europe (AFME)</t>
+  </si>
+  <si>
+    <t>https://www.afme.eu/events</t>
+  </si>
+  <si>
+    <t>Alternative Investment Management Association (AIMA)</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>https://www.aima.org/events.html</t>
+  </si>
+  <si>
+    <t>Managed Funds Association (MFA)</t>
+  </si>
+  <si>
+    <t>Hedge Funds</t>
+  </si>
+  <si>
+    <t>https://www.mfaalts.org/events/</t>
+  </si>
+  <si>
+    <t>Investment Company Institute (ICI)</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>https://www.ici.org/events</t>
+  </si>
+  <si>
+    <t>National Investor Relations Institute (NIRI)</t>
+  </si>
+  <si>
+    <t>Investor Relations</t>
+  </si>
+  <si>
+    <t>https://www.niri.org/education/events</t>
+  </si>
+  <si>
+    <t>The Conference Board</t>
+  </si>
+  <si>
+    <t>Corporate Governance</t>
+  </si>
+  <si>
+    <t>https://www.conference-board.org/events</t>
+  </si>
+  <si>
+    <t>Institute of Corporate Directors (ICD)</t>
+  </si>
+  <si>
+    <t>https://www.icd.ca/events</t>
+  </si>
+  <si>
+    <t>Institute of Company Secretaries of India (ICSI)</t>
+  </si>
+  <si>
+    <t>Corporate Law &amp; Governance</t>
+  </si>
+  <si>
+    <t>https://www.icsi.edu/events/</t>
+  </si>
+  <si>
+    <t>Chartered Governance Institute UK &amp; Ireland (CGI)</t>
+  </si>
+  <si>
+    <t>https://www.cgi.org.uk/events</t>
+  </si>
+  <si>
+    <t>European Corporate Governance Institute (ECGI)</t>
+  </si>
+  <si>
+    <t>https://ecgi.global/events</t>
+  </si>
+  <si>
+    <t>International Ombudsman Institute (IOI)</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>https://www.theioi.org/events</t>
+  </si>
+  <si>
+    <t>Society for Corporate Governance</t>
+  </si>
+  <si>
+    <t>https://www.societycorpgov.org/events</t>
+  </si>
+  <si>
+    <t>Licensing Executives Society International (LESI)</t>
+  </si>
+  <si>
+    <t>IP &amp; Commercialization</t>
+  </si>
+  <si>
+    <t>https://www.lesi.org/events</t>
+  </si>
+  <si>
+    <t>European Association of Tax Law Professors (EATLP)</t>
+  </si>
+  <si>
+    <t>https://www.eatlp.org/events</t>
+  </si>
+  <si>
+    <t>Tax Research Network (TRN)</t>
+  </si>
+  <si>
+    <t>Tax Research</t>
+  </si>
+  <si>
+    <t>https://www.taxresearch.org.uk/events/</t>
+  </si>
+  <si>
+    <t>Institute for Austrian and International Tax Law (WU Vienna)</t>
+  </si>
+  <si>
+    <t>https://www.wu.ac.at/en/taxlaw/news-events</t>
+  </si>
+  <si>
+    <t>Oxford University Centre for Business Taxation</t>
+  </si>
+  <si>
+    <t>https://www.sbs.ox.ac.uk/research/centres-and-initiatives/oxford-university-centre-business-taxation/events</t>
+  </si>
+  <si>
+    <t>Tax Justice Network</t>
+  </si>
+  <si>
+    <t>International Tax Policy</t>
+  </si>
+  <si>
+    <t>https://taxjustice.net/events/</t>
+  </si>
+  <si>
+    <t>National Association for Business Economics (NABE)</t>
+  </si>
+  <si>
+    <t>Economics &amp; Finance</t>
+  </si>
+  <si>
+    <t>https://www.nabe.com/NABE/Events</t>
+  </si>
+  <si>
+    <t>American Finance Association (AFA)</t>
+  </si>
+  <si>
+    <t>https://afajof.org/annual-meeting/</t>
+  </si>
+  <si>
+    <t>Western Finance Association (WFA)</t>
+  </si>
+  <si>
+    <t>https://westernfinance.org/conference</t>
+  </si>
+  <si>
+    <t>Eastern Finance Association (EFA)</t>
+  </si>
+  <si>
+    <t>https://www.easternfinance.org/annual-meeting</t>
+  </si>
+  <si>
+    <t>Southern Finance Association (SFA)</t>
+  </si>
+  <si>
+    <t>https://www.southernfinance.org/annual-meeting</t>
+  </si>
+  <si>
+    <t>European Finance Association (EFA)</t>
+  </si>
+  <si>
+    <t>https://europeanfinance.org/events/</t>
+  </si>
+  <si>
+    <t>Financial Intermediation Research Society (FIRS)</t>
+  </si>
+  <si>
+    <t>https://www.firsociety.org/conference</t>
+  </si>
+  <si>
+    <t>International Association of Credit Portfolio Managers (IACPM)</t>
+  </si>
+  <si>
+    <t>Banking &amp; Credit Risk</t>
+  </si>
+  <si>
+    <t>https://www.iacpm.org/events</t>
+  </si>
+  <si>
+    <t>Global Association of Central Counterparties (CCP Global)</t>
+  </si>
+  <si>
+    <t>Financial Markets</t>
+  </si>
+  <si>
+    <t>https://ccpglobal.org/events/</t>
+  </si>
+  <si>
+    <t>Mortgage Bankers Association (MBA)</t>
+  </si>
+  <si>
+    <t>https://www.mba.org/conferences-and-education</t>
+  </si>
+  <si>
+    <t>American Bankers Association (ABA Banking)</t>
+  </si>
+  <si>
+    <t>https://www.aba.com/training-events/events</t>
+  </si>
+  <si>
+    <t>Independent Community Bankers of America (ICBA)</t>
+  </si>
+  <si>
+    <t>https://www.icba.org/events</t>
+  </si>
+  <si>
+    <t>International Federation of Insolvency Professionals (INSOL Europe)</t>
+  </si>
+  <si>
+    <t>https://www.insol-europe.org/events</t>
+  </si>
+  <si>
+    <t>International Council for Commercial Arbitration (ICCA)</t>
+  </si>
+  <si>
+    <t>Arbitration</t>
+  </si>
+  <si>
+    <t>https://www.arbitration-icca.org/events</t>
+  </si>
+  <si>
+    <t>London Court of International Arbitration (LCIA)</t>
+  </si>
+  <si>
+    <t>https://www.lcia.org/events.aspx</t>
+  </si>
+  <si>
+    <t>Singapore International Arbitration Centre (SIAC)</t>
+  </si>
+  <si>
+    <t>https://siac.org.sg/events</t>
+  </si>
+  <si>
+    <t>Internal Revenue Service (IRS)</t>
+  </si>
+  <si>
+    <t>Tax Authority</t>
+  </si>
+  <si>
+    <t>https://www.irs.gov/businesses/small-businesses-self-employed/small-business-tax-workshops-meetings-and-seminars (IRS)</t>
+  </si>
+  <si>
+    <t>Inland Revenue Authority of Singapore (IRAS)</t>
+  </si>
+  <si>
+    <t>https://www.iras.gov.sg/news-events/events (Default)</t>
+  </si>
+  <si>
+    <t>U.S. Securities and Exchange Commission (SEC)</t>
+  </si>
+  <si>
+    <t>Securities Regulator</t>
+  </si>
+  <si>
+    <t>https://www.sec.gov/newsroom/meetings-events (SEC)</t>
+  </si>
+  <si>
+    <t>HM Revenue &amp; Customs (HMRC)</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>https://www.gov.uk/government/organisations/hm-revenue-customs</t>
+  </si>
+  <si>
+    <t>Australian Taxation Office (ATO)</t>
+  </si>
+  <si>
+    <t>https://www.ato.gov.au/news-and-media/events</t>
+  </si>
+  <si>
+    <t>Canada Revenue Agency (CRA)</t>
+  </si>
+  <si>
+    <t>https://www.canada.ca/en/revenue-agency/news/events.html</t>
+  </si>
+  <si>
+    <t>New Zealand Inland Revenue (IRD)</t>
+  </si>
+  <si>
+    <t>New Zealand</t>
+  </si>
+  <si>
+    <t>https://www.ird.govt.nz/news</t>
+  </si>
+  <si>
+    <t>South African Revenue Service (SARS)</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>https://www.sars.gov.za/media-room/events/</t>
+  </si>
+  <si>
+    <t>Federal Inland Revenue Service (FIRS)</t>
+  </si>
+  <si>
+    <t>Nigeria</t>
+  </si>
+  <si>
+    <t>https://www.firs.gov.ng/events</t>
+  </si>
+  <si>
+    <t>Federal Tax Authority (FTA)</t>
+  </si>
+  <si>
+    <t>UAE</t>
+  </si>
+  <si>
+    <t>https://tax.gov.ae/en/media.centre/events.aspx</t>
+  </si>
+  <si>
+    <t>European Securities and Markets Authority (ESMA)</t>
+  </si>
+  <si>
+    <t>European Union</t>
+  </si>
+  <si>
+    <t>https://www.esma.europa.eu/press-news/events</t>
+  </si>
+  <si>
+    <t>Financial Conduct Authority (FCA)</t>
+  </si>
+  <si>
+    <t>Financial Regulator</t>
+  </si>
+  <si>
+    <t>https://www.fca.org.uk/events</t>
+  </si>
+  <si>
+    <t>Australian Securities &amp; Investments Commission (ASIC)</t>
+  </si>
+  <si>
+    <t>Corporate &amp; Securities</t>
+  </si>
+  <si>
+    <t>https://asic.gov.au/about-asic/news-centre/events/</t>
+  </si>
+  <si>
+    <t>Monetary Authority of Singapore (MAS)</t>
+  </si>
+  <si>
+    <t>Central Bank &amp; Financial Regulator</t>
+  </si>
+  <si>
+    <t>https://www.mas.gov.sg/news/events</t>
+  </si>
+  <si>
+    <t>Bank of England</t>
+  </si>
+  <si>
+    <t>Central Bank</t>
+  </si>
+  <si>
+    <t>https://www.bankofengland.co.uk/events</t>
+  </si>
+  <si>
+    <t>European Central Bank (ECB)</t>
+  </si>
+  <si>
+    <t>https://www.ecb.europa.eu/press/conferences/html/index.en.html</t>
+  </si>
+  <si>
+    <t>Federal Reserve Board</t>
+  </si>
+  <si>
+    <t>https://www.federalreserve.gov/conferences.htm</t>
+  </si>
+  <si>
+    <t>Reserve Bank of Australia (RBA)</t>
+  </si>
+  <si>
+    <t>https://www.rba.gov.au/conferences/</t>
+  </si>
+  <si>
+    <t>Reserve Bank of New Zealand (RBNZ)</t>
+  </si>
+  <si>
+    <t>https://www.rbnz.govt.nz/news-and-events</t>
+  </si>
+  <si>
+    <t>Bank for International Settlements (BIS)</t>
+  </si>
+  <si>
+    <t>Central Banking</t>
+  </si>
+  <si>
+    <t>https://www.bis.org/events/</t>
+  </si>
+  <si>
+    <t>Financial Stability Board (FSB)</t>
+  </si>
+  <si>
+    <t>Financial Stability</t>
+  </si>
+  <si>
+    <t>https://www.fsb.org/events/</t>
+  </si>
+  <si>
+    <t>Organisation for Economic Co-operation and Development (OECD)</t>
+  </si>
+  <si>
+    <t>Tax &amp; Economics</t>
+  </si>
+  <si>
+    <t>https://www.oecd.org/events/</t>
+  </si>
+  <si>
+    <t>World Bank</t>
+  </si>
+  <si>
+    <t>Finance &amp; Development</t>
+  </si>
+  <si>
+    <t>https://live.worldbank.org/events</t>
+  </si>
+  <si>
+    <t>International Monetary Fund (IMF)</t>
+  </si>
+  <si>
+    <t>Finance &amp; Economics</t>
+  </si>
+  <si>
+    <t>https://www.imf.org/en/News/Seminars</t>
+  </si>
+  <si>
+    <t>United Nations Trade and Development (UNCTAD)</t>
+  </si>
+  <si>
+    <t>Trade &amp; Investment</t>
+  </si>
+  <si>
+    <t>https://unctad.org/meetings</t>
+  </si>
+  <si>
+    <t>International Organization of Securities Commissions (IOSCO)</t>
+  </si>
+  <si>
+    <t>Securities Regulation</t>
+  </si>
+  <si>
+    <t>https://www.iosco.org/events/</t>
+  </si>
+  <si>
+    <t>International Forum of Independent Audit Regulators (IFIAR)</t>
+  </si>
+  <si>
+    <t>Audit Regulation</t>
+  </si>
+  <si>
+    <t>https://www.ifiar.org/events/</t>
+  </si>
+  <si>
+    <t>Financial Action Task Force (FATF)</t>
+  </si>
+  <si>
+    <t>AML/CFT</t>
+  </si>
+  <si>
+    <t>https://www.fatf-gafi.org/en/home/events.html</t>
+  </si>
+  <si>
+    <t>Egmont Group of Financial Intelligence Units</t>
+  </si>
+  <si>
+    <t>https://egmontgroup.org/news-and-events/</t>
+  </si>
+  <si>
+    <t>Wolfsberg Group</t>
+  </si>
+  <si>
+    <t>Financial Crime &amp; Banking</t>
+  </si>
+  <si>
+    <t>https://www.wolfsberg-group.org/events</t>
+  </si>
+  <si>
+    <t>SWIFT</t>
+  </si>
+  <si>
+    <t>Payments</t>
+  </si>
+  <si>
+    <t>https://www.swift.com/events</t>
+  </si>
+  <si>
+    <t>Nacha</t>
+  </si>
+  <si>
+    <t>https://www.nacha.org/events</t>
+  </si>
+  <si>
+    <t>PCI Security Standards Council</t>
+  </si>
+  <si>
+    <t>Payment Security</t>
+  </si>
+  <si>
+    <t>https://www.pcisecuritystandards.org/events/</t>
+  </si>
+  <si>
+    <t>FS-ISAC</t>
+  </si>
+  <si>
+    <t>Cybersecurity (Financial Services)</t>
+  </si>
+  <si>
+    <t>https://www.fsisac.com/events</t>
+  </si>
+  <si>
+    <t>OpenID Foundation</t>
+  </si>
+  <si>
+    <t>Digital Identity</t>
+  </si>
+  <si>
+    <t>https://openid.net/events/</t>
+  </si>
+  <si>
+    <t>FINOS</t>
+  </si>
+  <si>
+    <t>FinTech</t>
+  </si>
+  <si>
+    <t>https://www.finos.org/events</t>
+  </si>
+  <si>
+    <t>Global Digital Finance (GDF)</t>
+  </si>
+  <si>
+    <t>Digital Assets</t>
+  </si>
+  <si>
+    <t>https://www.gdf.io/events</t>
+  </si>
+  <si>
+    <t>Institute of International Finance (IIF)</t>
+  </si>
+  <si>
+    <t>Global Finance</t>
+  </si>
+  <si>
+    <t>https://www.iif.com/Events</t>
+  </si>
+  <si>
+    <t>International Finance Corporation (IFC)</t>
+  </si>
+  <si>
+    <t>Development Finance</t>
+  </si>
+  <si>
+    <t>https://www.ifc.org/en/events</t>
+  </si>
+  <si>
+    <t>Geneva Association</t>
+  </si>
+  <si>
+    <t>Insurance Research</t>
+  </si>
+  <si>
+    <t>https://www.genevaassociation.org/events</t>
+  </si>
+  <si>
+    <t>International Actuarial Association (IAA)</t>
+  </si>
+  <si>
+    <t>Actuarial</t>
+  </si>
+  <si>
+    <t>https://www.actuaries.org/events</t>
+  </si>
+  <si>
+    <t>Chartered Institute of Procurement &amp; Supply (CIPS)</t>
+  </si>
+  <si>
+    <t>Procurement</t>
+  </si>
+  <si>
+    <t>https://www.cips.org/events</t>
+  </si>
+  <si>
+    <t>Institute for Supply Management (ISM)</t>
+  </si>
+  <si>
+    <t>Supply Chain &amp; Procurement</t>
+  </si>
+  <si>
+    <t>https://www.ismworld.org/events/</t>
+  </si>
+  <si>
+    <t>International Federation of Purchasing and Supply Management (IFPSM)</t>
+  </si>
+  <si>
+    <t>https://www.ifpsm.org/events</t>
+  </si>
+  <si>
+    <t>International Trade Administration (ITA)</t>
+  </si>
+  <si>
+    <t>International Trade</t>
+  </si>
+  <si>
+    <t>https://www.trade.gov/events</t>
+  </si>
+  <si>
+    <t>U.S. Commercial Service</t>
+  </si>
+  <si>
+    <t>Export &amp; Trade</t>
+  </si>
+  <si>
+    <t>https://www.trade.gov/trade-events</t>
+  </si>
+  <si>
+    <t>International Association of Business Communicators (IABC)</t>
+  </si>
+  <si>
+    <t>Corporate Communications &amp; Governance</t>
+  </si>
+  <si>
+    <t>https://www.iabc.com/events/</t>
+  </si>
+  <si>
+    <t>European Institute of Public Administration (EIPA)</t>
+  </si>
+  <si>
+    <t>Public Policy &amp; Governance</t>
+  </si>
+  <si>
+    <t>https://www.eipa.eu/events/</t>
+  </si>
+  <si>
+    <t>Tax Institute of Hong Kong</t>
+  </si>
+  <si>
+    <t>https://www.tihk.org.hk/events</t>
+  </si>
+  <si>
+    <t>Tax Institute of New Zealand</t>
+  </si>
+  <si>
+    <t>https://taxinstitute.org.nz/events</t>
+  </si>
+  <si>
+    <t>Irish Tax Institute</t>
+  </si>
+  <si>
+    <t>https://taxinstitute.ie/events</t>
+  </si>
+  <si>
+    <t>Institute of Indirect Taxation</t>
+  </si>
+  <si>
+    <t>Indirect Tax</t>
+  </si>
+  <si>
+    <t>https://www.iot.org.uk/events</t>
+  </si>
+  <si>
+    <t>Canadian Tax Foundation</t>
+  </si>
+  <si>
+    <t>https://www.ctf.ca/ctfweb/en/events.aspx</t>
+  </si>
+  <si>
+    <t>Canadian Taxpayers Federation</t>
+  </si>
+  <si>
+    <t>Tax Policy</t>
+  </si>
+  <si>
+    <t>https://www.taxpayer.com/events</t>
+  </si>
+  <si>
+    <t>International VAT Association (IVA)</t>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <t>https://www.vatassociation.org/events</t>
+  </si>
+  <si>
+    <t>Association of European VAT Professionals (AEVAT)</t>
+  </si>
+  <si>
+    <t>https://www.aevat.eu/events</t>
+  </si>
+  <si>
+    <t>International Customs Law Academy</t>
+  </si>
+  <si>
+    <t>https://www.customslawacademy.org/events</t>
+  </si>
+  <si>
+    <t>Customs Practitioners Group UK</t>
+  </si>
+  <si>
+    <t>https://www.customspractitionersgroup.uk/events</t>
+  </si>
+  <si>
+    <t>Law Council of New Zealand</t>
+  </si>
+  <si>
+    <t>https://www.lawsociety.org.nz/professional-practice/events/</t>
+  </si>
+  <si>
+    <t>Canadian Bar Association</t>
+  </si>
+  <si>
+    <t>https://www.cba.org/PD-Events</t>
+  </si>
+  <si>
+    <t>New York State Bar Association</t>
+  </si>
+  <si>
+    <t>https://nysba.org/events/</t>
+  </si>
+  <si>
+    <t>California Lawyers Association</t>
+  </si>
+  <si>
+    <t>https://calawyers.org/events/</t>
+  </si>
+  <si>
+    <t>Chicago Bar Association</t>
+  </si>
+  <si>
+    <t>https://www.chicagobar.org/events</t>
+  </si>
+  <si>
+    <t>International Association of Lawyers (UIA)</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>https://www.uianet.org/en/events</t>
+  </si>
+  <si>
+    <t>European Company Lawyers Association</t>
+  </si>
+  <si>
+    <t>Corporate Law</t>
+  </si>
+  <si>
+    <t>https://www.ecla.online/events</t>
+  </si>
+  <si>
+    <t>Hong Kong International Arbitration Centre</t>
+  </si>
+  <si>
+    <t>https://www.hkiac.org/events</t>
+  </si>
+  <si>
+    <t>Dubai International Arbitration Centre</t>
+  </si>
+  <si>
+    <t>https://www.diac.ae/events</t>
+  </si>
+  <si>
+    <t>Financial Executives Networking Group</t>
+  </si>
+  <si>
+    <t>https://www.feng.org/events</t>
+  </si>
+  <si>
+    <t>Treasury Management Association of Singapore</t>
+  </si>
+  <si>
+    <t>https://www.tmas.org.sg/events</t>
+  </si>
+  <si>
+    <t>European Association of Corporate Treasurers</t>
+  </si>
+  <si>
+    <t>https://www.eact.eu/events</t>
+  </si>
+  <si>
+    <t>Investment Association</t>
+  </si>
+  <si>
+    <t>https://www.theia.org/events</t>
+  </si>
+  <si>
+    <t>Institutional Limited Partners Association</t>
+  </si>
+  <si>
+    <t>Private Equity</t>
+  </si>
+  <si>
+    <t>https://ilpa.org/events/</t>
+  </si>
+  <si>
+    <t>Invest Europe</t>
+  </si>
+  <si>
+    <t>Private Equity &amp; VC</t>
+  </si>
+  <si>
+    <t>https://www.investeurope.eu/events/</t>
+  </si>
+  <si>
+    <t>Private Equity CFO Association</t>
+  </si>
+  <si>
+    <t>https://www.privateequitycfo.com/events</t>
+  </si>
+  <si>
+    <t>Global Impact Investing Network (GIIN)</t>
+  </si>
+  <si>
+    <t>Impact Investing</t>
+  </si>
+  <si>
+    <t>https://thegiin.org/events/</t>
+  </si>
+  <si>
+    <t>FinTech Australia</t>
+  </si>
+  <si>
+    <t>https://www.fintechaustralia.org.au/events</t>
+  </si>
+  <si>
+    <t>Innovate Finance</t>
+  </si>
+  <si>
+    <t>https://www.innovatefinance.com/events/</t>
+  </si>
+  <si>
+    <t>Singapore FinTech Association</t>
+  </si>
+  <si>
+    <t>https://singaporefintech.org/events/</t>
+  </si>
+  <si>
+    <t>FinTech Association of Hong Kong</t>
+  </si>
+  <si>
+    <t>https://www.ftahk.org/events</t>
+  </si>
+  <si>
+    <t>Global Legal Entity Identifier Foundation (GLEIF)</t>
+  </si>
+  <si>
+    <t>Financial Infrastructure</t>
+  </si>
+  <si>
+    <t>https://www.gleif.org/en/events</t>
+  </si>
+  <si>
+    <t>International Association of Credit Rating Agencies</t>
+  </si>
+  <si>
+    <t>Credit Markets</t>
+  </si>
+  <si>
+    <t>https://www.iacra.org/events</t>
+  </si>
+  <si>
+    <t>Institute of Credit Management</t>
+  </si>
+  <si>
+    <t>Credit Management</t>
+  </si>
+  <si>
+    <t>https://www.cicm.com/events/</t>
+  </si>
+  <si>
+    <t>Credit Institute of Canada</t>
+  </si>
+  <si>
+    <t>https://creditedu.org/events</t>
+  </si>
+  <si>
+    <t>International Federation of Compliance Associations</t>
+  </si>
+  <si>
+    <t>https://www.ifca.org/events</t>
+  </si>
+  <si>
+    <t>Association of Governance, Risk &amp; Compliance (AGRC)</t>
+  </si>
+  <si>
+    <t>GRC</t>
+  </si>
+  <si>
+    <t>https://www.theagrc.org/events</t>
+  </si>
+  <si>
+    <t>Global Reporting Initiative (GRI)</t>
   </si>
   <si>
     <t>ESG</t>
   </si>
   <si>
-    <t>AGA</t>
-  </si>
-  <si>
-    <t>Government Finance</t>
-  </si>
-  <si>
-    <t>https://www.agacgfm.org/Events.aspx</t>
-  </si>
-  <si>
-    <t>NASBA</t>
-  </si>
-  <si>
-    <t>https://nasba.org/events/</t>
-  </si>
-  <si>
-    <t>IMA</t>
-  </si>
-  <si>
-    <t>Management Accounting</t>
-  </si>
-  <si>
-    <t>https://www.imanet.org/events</t>
-  </si>
-  <si>
-    <t>FMA</t>
-  </si>
-  <si>
-    <t>https://fma.org/events</t>
-  </si>
-  <si>
-    <t>Global Finance Conferences</t>
-  </si>
-  <si>
-    <t>https://globalfinanceconference.com/conference/</t>
-  </si>
-  <si>
-    <t>EAA</t>
-  </si>
-  <si>
-    <t>Europe</t>
-  </si>
-  <si>
-    <t>https://eaa-online.org/events/</t>
-  </si>
-  <si>
-    <t>EFMA</t>
-  </si>
-  <si>
-    <t>https://www.efmaefm.org/events/</t>
-  </si>
-  <si>
-    <t>IAAER</t>
-  </si>
-  <si>
-    <t>https://www.iaaer.org/events</t>
-  </si>
-  <si>
-    <t>ICV</t>
-  </si>
-  <si>
-    <t>Controlling</t>
-  </si>
-  <si>
-    <t>https://icv-controlling.com/en/events/</t>
-  </si>
-  <si>
-    <t>ACT</t>
-  </si>
-  <si>
-    <t>https://www.treasurers.org/events</t>
-  </si>
-  <si>
-    <t>EuroFinance</t>
-  </si>
-  <si>
-    <t>https://www.eurofinance.com/events</t>
-  </si>
-  <si>
-    <t>ABS Singapore</t>
-  </si>
-  <si>
-    <t>https://abs.org.sg/events</t>
-  </si>
-  <si>
-    <t>IAFEI</t>
-  </si>
-  <si>
-    <t>https://iafei.org/events</t>
-  </si>
-  <si>
-    <t>IBE</t>
-  </si>
-  <si>
-    <t>Ethics</t>
-  </si>
-  <si>
-    <t>https://www.ibe.org.uk/events.html</t>
-  </si>
-  <si>
-    <t>ECI</t>
-  </si>
-  <si>
-    <t>https://www.ethics.org/events/</t>
-  </si>
-  <si>
-    <t>NAEA</t>
-  </si>
-  <si>
-    <t>https://www.naea.org/events/</t>
-  </si>
-  <si>
-    <t>International Association of Insurance Supervisors (IAIS)</t>
-  </si>
-  <si>
-    <t>Insurance Regulation</t>
-  </si>
-  <si>
-    <t>https://www.iaisweb.org/events/</t>
-  </si>
-  <si>
-    <t>International Association of Financial Crimes Investigators (IAFCI)</t>
-  </si>
-  <si>
-    <t>Financial Crime</t>
-  </si>
-  <si>
-    <t>https://www.iafci.org/events</t>
-  </si>
-  <si>
-    <t>Association of Certified Anti-Money Laundering Specialists (ACAMS)</t>
-  </si>
-  <si>
-    <t>AML &amp; Compliance</t>
-  </si>
-  <si>
-    <t>https://www.acams.org/en/events</t>
-  </si>
-  <si>
-    <t>Association of Certified Sanctions Specialists (ACSS)</t>
-  </si>
-  <si>
-    <t>Sanctions</t>
-  </si>
-  <si>
-    <t>International Association of Privacy Professionals Asia (IAPP Asia)</t>
-  </si>
-  <si>
-    <t>Association of Corporate Investigators (ACI)</t>
-  </si>
-  <si>
-    <t>Corporate Investigations</t>
-  </si>
-  <si>
-    <t>https://www.aci.org.uk/events</t>
-  </si>
-  <si>
-    <t>Institute of Certified Bookkeepers (ICB)</t>
-  </si>
-  <si>
-    <t>Bookkeeping</t>
-  </si>
-  <si>
-    <t>https://www.bookkeepers.org.uk/training-and-events</t>
-  </si>
-  <si>
-    <t>Association of International Certified Professional Accountants - UK</t>
-  </si>
-  <si>
-    <t>https://www.aicpa-cima.com/events</t>
-  </si>
-  <si>
-    <t>European Banking Federation (EBF)</t>
-  </si>
-  <si>
-    <t>https://www.ebf.eu/events/</t>
-  </si>
-  <si>
-    <t>European Association of Co-operative Banks (EACB)</t>
-  </si>
-  <si>
-    <t>https://www.eacb.coop/en/events.html</t>
-  </si>
-  <si>
-    <t>International Securities Lending Association (ISLA)</t>
-  </si>
-  <si>
-    <t>https://www.islaemea.org/events/</t>
-  </si>
-  <si>
-    <t>Association for Financial Markets in Europe (AFME)</t>
-  </si>
-  <si>
-    <t>https://www.afme.eu/events</t>
-  </si>
-  <si>
-    <t>Alternative Investment Management Association (AIMA)</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>https://www.aima.org/events.html</t>
-  </si>
-  <si>
-    <t>Managed Funds Association (MFA)</t>
-  </si>
-  <si>
-    <t>Hedge Funds</t>
-  </si>
-  <si>
-    <t>https://www.mfaalts.org/events/</t>
-  </si>
-  <si>
-    <t>Investment Company Institute (ICI)</t>
-  </si>
-  <si>
-    <t>Asset Management</t>
-  </si>
-  <si>
-    <t>https://www.ici.org/events</t>
-  </si>
-  <si>
-    <t>National Investor Relations Institute (NIRI)</t>
-  </si>
-  <si>
-    <t>Investor Relations</t>
-  </si>
-  <si>
-    <t>https://www.niri.org/education/events</t>
-  </si>
-  <si>
-    <t>The Conference Board</t>
-  </si>
-  <si>
-    <t>Corporate Governance</t>
-  </si>
-  <si>
-    <t>https://www.conference-board.org/events</t>
-  </si>
-  <si>
-    <t>Institute of Corporate Directors (ICD)</t>
-  </si>
-  <si>
-    <t>https://www.icd.ca/events</t>
-  </si>
-  <si>
-    <t>Institute of Company Secretaries of India (ICSI)</t>
-  </si>
-  <si>
-    <t>Corporate Law &amp; Governance</t>
-  </si>
-  <si>
-    <t>https://www.icsi.edu/events/</t>
-  </si>
-  <si>
-    <t>Chartered Governance Institute UK &amp; Ireland (CGI)</t>
-  </si>
-  <si>
-    <t>https://www.cgi.org.uk/events</t>
-  </si>
-  <si>
-    <t>European Corporate Governance Institute (ECGI)</t>
-  </si>
-  <si>
-    <t>https://ecgi.global/events</t>
-  </si>
-  <si>
-    <t>International Ombudsman Institute (IOI)</t>
-  </si>
-  <si>
-    <t>Austria</t>
-  </si>
-  <si>
-    <t>https://www.theioi.org/events</t>
-  </si>
-  <si>
-    <t>Society for Corporate Governance</t>
-  </si>
-  <si>
-    <t>https://www.societycorpgov.org/events</t>
-  </si>
-  <si>
-    <t>International Association for Contract &amp; Commercial Management (WorldCC)</t>
-  </si>
-  <si>
-    <t>Commercial Contracts</t>
-  </si>
-  <si>
-    <t>Licensing Executives Society International (LESI)</t>
-  </si>
-  <si>
-    <t>IP &amp; Commercialization</t>
-  </si>
-  <si>
-    <t>https://www.lesi.org/events</t>
-  </si>
-  <si>
-    <t>International Fiscal Documentation Foundation (IFA Branches Events)</t>
-  </si>
-  <si>
-    <t>European Association of Tax Law Professors (EATLP)</t>
-  </si>
-  <si>
-    <t>https://www.eatlp.org/events</t>
-  </si>
-  <si>
-    <t>Tax Research Network (TRN)</t>
-  </si>
-  <si>
-    <t>Tax Research</t>
-  </si>
-  <si>
-    <t>https://www.taxresearch.org.uk/events/</t>
-  </si>
-  <si>
-    <t>Institute for Austrian and International Tax Law (WU Vienna)</t>
-  </si>
-  <si>
-    <t>https://www.wu.ac.at/en/taxlaw/news-events</t>
-  </si>
-  <si>
-    <t>Oxford University Centre for Business Taxation</t>
-  </si>
-  <si>
-    <t>https://www.sbs.ox.ac.uk/research/centres-and-initiatives/oxford-university-centre-business-taxation/events</t>
-  </si>
-  <si>
-    <t>Vienna University of Economics &amp; Business (WU) Transfer Pricing Center</t>
-  </si>
-  <si>
-    <t>Transfer Pricing</t>
-  </si>
-  <si>
-    <t>International Bureau of Fiscal Documentation Asia (IBFD Asia)</t>
-  </si>
-  <si>
-    <t>Tax Justice Network</t>
-  </si>
-  <si>
-    <t>International Tax Policy</t>
-  </si>
-  <si>
-    <t>https://taxjustice.net/events/</t>
-  </si>
-  <si>
-    <t>National Association for Business Economics (NABE)</t>
-  </si>
-  <si>
-    <t>Economics &amp; Finance</t>
-  </si>
-  <si>
-    <t>https://www.nabe.com/NABE/Events</t>
-  </si>
-  <si>
-    <t>American Finance Association (AFA)</t>
-  </si>
-  <si>
-    <t>https://afajof.org/annual-meeting/</t>
-  </si>
-  <si>
-    <t>Western Finance Association (WFA)</t>
-  </si>
-  <si>
-    <t>https://westernfinance.org/conference</t>
-  </si>
-  <si>
-    <t>Eastern Finance Association (EFA)</t>
-  </si>
-  <si>
-    <t>https://www.easternfinance.org/annual-meeting</t>
-  </si>
-  <si>
-    <t>Southern Finance Association (SFA)</t>
-  </si>
-  <si>
-    <t>https://www.southernfinance.org/annual-meeting</t>
-  </si>
-  <si>
-    <t>European Finance Association (EFA)</t>
-  </si>
-  <si>
-    <t>https://europeanfinance.org/events/</t>
-  </si>
-  <si>
-    <t>Financial Intermediation Research Society (FIRS)</t>
-  </si>
-  <si>
-    <t>https://www.firsociety.org/conference</t>
-  </si>
-  <si>
-    <t>International Association of Credit Portfolio Managers (IACPM)</t>
-  </si>
-  <si>
-    <t>Banking &amp; Credit Risk</t>
-  </si>
-  <si>
-    <t>https://www.iacpm.org/events</t>
-  </si>
-  <si>
-    <t>Global Association of Central Counterparties (CCP Global)</t>
-  </si>
-  <si>
-    <t>Financial Markets</t>
-  </si>
-  <si>
-    <t>https://ccpglobal.org/events/</t>
-  </si>
-  <si>
-    <t>International Association of Deposit Insurers Asia-Pacific Forum</t>
-  </si>
-  <si>
-    <t>Mortgage Bankers Association (MBA)</t>
-  </si>
-  <si>
-    <t>https://www.mba.org/conferences-and-education</t>
-  </si>
-  <si>
-    <t>American Bankers Association (ABA Banking)</t>
-  </si>
-  <si>
-    <t>https://www.aba.com/training-events/events</t>
-  </si>
-  <si>
-    <t>Independent Community Bankers of America (ICBA)</t>
-  </si>
-  <si>
-    <t>https://www.icba.org/events</t>
-  </si>
-  <si>
-    <t>International Federation of Insolvency Professionals (INSOL Europe)</t>
-  </si>
-  <si>
-    <t>https://www.insol-europe.org/events</t>
-  </si>
-  <si>
-    <t>International Council for Commercial Arbitration (ICCA)</t>
-  </si>
-  <si>
-    <t>Arbitration</t>
-  </si>
-  <si>
-    <t>https://www.arbitration-icca.org/events</t>
-  </si>
-  <si>
-    <t>London Court of International Arbitration (LCIA)</t>
-  </si>
-  <si>
-    <t>https://www.lcia.org/events.aspx</t>
-  </si>
-  <si>
-    <t>Singapore International Arbitration Centre (SIAC)</t>
-  </si>
-  <si>
-    <t>https://siac.org.sg/events</t>
-  </si>
-  <si>
-    <t>Internal Revenue Service (IRS)</t>
-  </si>
-  <si>
-    <t>Tax Authority</t>
-  </si>
-  <si>
-    <t>https://www.irs.gov/businesses/small-businesses-self-employed/small-business-tax-workshops-meetings-and-seminars (IRS)</t>
-  </si>
-  <si>
-    <t>Inland Revenue Authority of Singapore (IRAS)</t>
-  </si>
-  <si>
-    <t>https://www.iras.gov.sg/news-events/events (Default)</t>
-  </si>
-  <si>
-    <t>U.S. Securities and Exchange Commission (SEC)</t>
-  </si>
-  <si>
-    <t>Securities Regulator</t>
-  </si>
-  <si>
-    <t>https://www.sec.gov/newsroom/meetings-events (SEC)</t>
-  </si>
-  <si>
-    <t>HM Revenue &amp; Customs (HMRC)</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>https://www.gov.uk/government/organisations/hm-revenue-customs</t>
-  </si>
-  <si>
-    <t>Australian Taxation Office (ATO)</t>
-  </si>
-  <si>
-    <t>https://www.ato.gov.au/news-and-media/events</t>
-  </si>
-  <si>
-    <t>Canada Revenue Agency (CRA)</t>
-  </si>
-  <si>
-    <t>https://www.canada.ca/en/revenue-agency/news/events.html</t>
-  </si>
-  <si>
-    <t>New Zealand Inland Revenue (IRD)</t>
-  </si>
-  <si>
-    <t>New Zealand</t>
-  </si>
-  <si>
-    <t>https://www.ird.govt.nz/news</t>
-  </si>
-  <si>
-    <t>South African Revenue Service (SARS)</t>
-  </si>
-  <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>https://www.sars.gov.za/media-room/events/</t>
-  </si>
-  <si>
-    <t>Federal Inland Revenue Service (FIRS)</t>
-  </si>
-  <si>
-    <t>Nigeria</t>
-  </si>
-  <si>
-    <t>https://www.firs.gov.ng/events</t>
-  </si>
-  <si>
-    <t>Federal Tax Authority (FTA)</t>
-  </si>
-  <si>
-    <t>UAE</t>
-  </si>
-  <si>
-    <t>https://tax.gov.ae/en/media.centre/events.aspx</t>
-  </si>
-  <si>
-    <t>European Securities and Markets Authority (ESMA)</t>
-  </si>
-  <si>
-    <t>European Union</t>
-  </si>
-  <si>
-    <t>https://www.esma.europa.eu/press-news/events</t>
-  </si>
-  <si>
-    <t>Financial Conduct Authority (FCA)</t>
-  </si>
-  <si>
-    <t>Financial Regulator</t>
-  </si>
-  <si>
-    <t>https://www.fca.org.uk/events</t>
-  </si>
-  <si>
-    <t>Australian Securities &amp; Investments Commission (ASIC)</t>
-  </si>
-  <si>
-    <t>Corporate &amp; Securities</t>
-  </si>
-  <si>
-    <t>https://asic.gov.au/about-asic/news-centre/events/</t>
-  </si>
-  <si>
-    <t>Monetary Authority of Singapore (MAS)</t>
-  </si>
-  <si>
-    <t>Central Bank &amp; Financial Regulator</t>
-  </si>
-  <si>
-    <t>https://www.mas.gov.sg/news/events</t>
-  </si>
-  <si>
-    <t>Bank of England</t>
-  </si>
-  <si>
-    <t>Central Bank</t>
-  </si>
-  <si>
-    <t>https://www.bankofengland.co.uk/events</t>
-  </si>
-  <si>
-    <t>European Central Bank (ECB)</t>
-  </si>
-  <si>
-    <t>https://www.ecb.europa.eu/press/conferences/html/index.en.html</t>
-  </si>
-  <si>
-    <t>Federal Reserve Board</t>
-  </si>
-  <si>
-    <t>https://www.federalreserve.gov/conferences.htm</t>
-  </si>
-  <si>
-    <t>Reserve Bank of Australia (RBA)</t>
-  </si>
-  <si>
-    <t>https://www.rba.gov.au/conferences/</t>
-  </si>
-  <si>
-    <t>Reserve Bank of New Zealand (RBNZ)</t>
-  </si>
-  <si>
-    <t>https://www.rbnz.govt.nz/news-and-events</t>
-  </si>
-  <si>
-    <t>Bank for International Settlements (BIS)</t>
-  </si>
-  <si>
-    <t>Central Banking</t>
-  </si>
-  <si>
-    <t>https://www.bis.org/events/</t>
-  </si>
-  <si>
-    <t>Financial Stability Board (FSB)</t>
-  </si>
-  <si>
-    <t>Financial Stability</t>
-  </si>
-  <si>
-    <t>https://www.fsb.org/events/</t>
-  </si>
-  <si>
-    <t>Organisation for Economic Co-operation and Development (OECD)</t>
-  </si>
-  <si>
-    <t>Tax &amp; Economics</t>
-  </si>
-  <si>
-    <t>https://www.oecd.org/events/</t>
-  </si>
-  <si>
-    <t>World Bank</t>
-  </si>
-  <si>
-    <t>Finance &amp; Development</t>
-  </si>
-  <si>
-    <t>https://live.worldbank.org/events</t>
-  </si>
-  <si>
-    <t>International Monetary Fund (IMF)</t>
-  </si>
-  <si>
-    <t>Finance &amp; Economics</t>
-  </si>
-  <si>
-    <t>https://www.imf.org/en/News/Seminars</t>
-  </si>
-  <si>
-    <t>United Nations Trade and Development (UNCTAD)</t>
-  </si>
-  <si>
-    <t>Trade &amp; Investment</t>
-  </si>
-  <si>
-    <t>https://unctad.org/meetings</t>
-  </si>
-  <si>
-    <t>International Organization of Securities Commissions (IOSCO)</t>
-  </si>
-  <si>
-    <t>Securities Regulation</t>
-  </si>
-  <si>
-    <t>https://www.iosco.org/events/</t>
-  </si>
-  <si>
-    <t>International Forum of Independent Audit Regulators (IFIAR)</t>
-  </si>
-  <si>
-    <t>Audit Regulation</t>
-  </si>
-  <si>
-    <t>https://www.ifiar.org/events/</t>
-  </si>
-  <si>
-    <t>Financial Action Task Force (FATF)</t>
-  </si>
-  <si>
-    <t>AML/CFT</t>
-  </si>
-  <si>
-    <t>https://www.fatf-gafi.org/en/home/events.html</t>
-  </si>
-  <si>
-    <t>Egmont Group of Financial Intelligence Units</t>
-  </si>
-  <si>
-    <t>https://egmontgroup.org/news-and-events/</t>
-  </si>
-  <si>
-    <t>Wolfsberg Group</t>
-  </si>
-  <si>
-    <t>Financial Crime &amp; Banking</t>
-  </si>
-  <si>
-    <t>https://www.wolfsberg-group.org/events</t>
-  </si>
-  <si>
-    <t>SWIFT</t>
-  </si>
-  <si>
-    <t>Payments</t>
-  </si>
-  <si>
-    <t>https://www.swift.com/events</t>
-  </si>
-  <si>
-    <t>Nacha</t>
-  </si>
-  <si>
-    <t>https://www.nacha.org/events</t>
-  </si>
-  <si>
-    <t>PCI Security Standards Council</t>
-  </si>
-  <si>
-    <t>Payment Security</t>
-  </si>
-  <si>
-    <t>https://www.pcisecuritystandards.org/events/</t>
-  </si>
-  <si>
-    <t>FS-ISAC</t>
-  </si>
-  <si>
-    <t>Cybersecurity (Financial Services)</t>
-  </si>
-  <si>
-    <t>https://www.fsisac.com/events</t>
-  </si>
-  <si>
-    <t>OpenID Foundation</t>
-  </si>
-  <si>
-    <t>Digital Identity</t>
-  </si>
-  <si>
-    <t>https://openid.net/events/</t>
-  </si>
-  <si>
-    <t>FINOS</t>
-  </si>
-  <si>
-    <t>FinTech</t>
-  </si>
-  <si>
-    <t>https://www.finos.org/events</t>
-  </si>
-  <si>
-    <t>Global Digital Finance (GDF)</t>
-  </si>
-  <si>
-    <t>Digital Assets</t>
-  </si>
-  <si>
-    <t>https://www.gdf.io/events</t>
-  </si>
-  <si>
-    <t>Institute of International Finance (IIF)</t>
-  </si>
-  <si>
-    <t>Global Finance</t>
-  </si>
-  <si>
-    <t>https://www.iif.com/Events</t>
-  </si>
-  <si>
-    <t>International Finance Corporation (IFC)</t>
-  </si>
-  <si>
-    <t>Development Finance</t>
-  </si>
-  <si>
-    <t>https://www.ifc.org/en/events</t>
-  </si>
-  <si>
-    <t>International Association of Insurance Supervisors (regional events)</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>Geneva Association</t>
-  </si>
-  <si>
-    <t>Insurance Research</t>
-  </si>
-  <si>
-    <t>https://www.genevaassociation.org/events</t>
-  </si>
-  <si>
-    <t>International Actuarial Association (IAA)</t>
-  </si>
-  <si>
-    <t>Actuarial</t>
-  </si>
-  <si>
-    <t>https://www.actuaries.org/events</t>
-  </si>
-  <si>
-    <t>Chartered Institute of Procurement &amp; Supply (CIPS)</t>
-  </si>
-  <si>
-    <t>Procurement</t>
-  </si>
-  <si>
-    <t>https://www.cips.org/events</t>
-  </si>
-  <si>
-    <t>Institute for Supply Management (ISM)</t>
-  </si>
-  <si>
-    <t>Supply Chain &amp; Procurement</t>
-  </si>
-  <si>
-    <t>https://www.ismworld.org/events/</t>
-  </si>
-  <si>
-    <t>World Commerce &amp; Contracting Academy</t>
-  </si>
-  <si>
-    <t>International Federation of Purchasing and Supply Management (IFPSM)</t>
-  </si>
-  <si>
-    <t>https://www.ifpsm.org/events</t>
-  </si>
-  <si>
-    <t>International Trade Administration (ITA)</t>
-  </si>
-  <si>
-    <t>International Trade</t>
-  </si>
-  <si>
-    <t>https://www.trade.gov/events</t>
-  </si>
-  <si>
-    <t>U.S. Commercial Service</t>
-  </si>
-  <si>
-    <t>Export &amp; Trade</t>
-  </si>
-  <si>
-    <t>https://www.trade.gov/trade-events</t>
-  </si>
-  <si>
-    <t>International Association of Business Communicators (IABC)</t>
-  </si>
-  <si>
-    <t>Corporate Communications &amp; Governance</t>
-  </si>
-  <si>
-    <t>https://www.iabc.com/events/</t>
-  </si>
-  <si>
-    <t>European Institute of Public Administration (EIPA)</t>
-  </si>
-  <si>
-    <t>Public Policy &amp; Governance</t>
-  </si>
-  <si>
-    <t>https://www.eipa.eu/events/</t>
-  </si>
-  <si>
-    <t>Tax Institute of Hong Kong</t>
-  </si>
-  <si>
-    <t>https://www.tihk.org.hk/events</t>
-  </si>
-  <si>
-    <t>Tax Institute of New Zealand</t>
-  </si>
-  <si>
-    <t>https://taxinstitute.org.nz/events</t>
-  </si>
-  <si>
-    <t>Irish Tax Institute</t>
-  </si>
-  <si>
-    <t>https://taxinstitute.ie/events</t>
-  </si>
-  <si>
-    <t>Institute of Indirect Taxation</t>
-  </si>
-  <si>
-    <t>Indirect Tax</t>
-  </si>
-  <si>
-    <t>https://www.iot.org.uk/events</t>
-  </si>
-  <si>
-    <t>Canadian Tax Foundation</t>
-  </si>
-  <si>
-    <t>https://www.ctf.ca/ctfweb/en/events.aspx</t>
-  </si>
-  <si>
-    <t>Canadian Taxpayers Federation</t>
-  </si>
-  <si>
-    <t>Tax Policy</t>
-  </si>
-  <si>
-    <t>https://www.taxpayer.com/events</t>
-  </si>
-  <si>
-    <t>International VAT Association (IVA)</t>
-  </si>
-  <si>
-    <t>VAT</t>
-  </si>
-  <si>
-    <t>https://www.vatassociation.org/events</t>
-  </si>
-  <si>
-    <t>Association of European VAT Professionals (AEVAT)</t>
-  </si>
-  <si>
-    <t>https://www.aevat.eu/events</t>
-  </si>
-  <si>
-    <t>International Customs Law Academy</t>
-  </si>
-  <si>
-    <t>https://www.customslawacademy.org/events</t>
-  </si>
-  <si>
-    <t>Customs Practitioners Group UK</t>
-  </si>
-  <si>
-    <t>https://www.customspractitionersgroup.uk/events</t>
-  </si>
-  <si>
-    <t>Law Council of New Zealand</t>
-  </si>
-  <si>
-    <t>https://www.lawsociety.org.nz/professional-practice/events/</t>
-  </si>
-  <si>
-    <t>Canadian Bar Association</t>
-  </si>
-  <si>
-    <t>https://www.cba.org/PD-Events</t>
-  </si>
-  <si>
-    <t>New York State Bar Association</t>
-  </si>
-  <si>
-    <t>https://nysba.org/events/</t>
-  </si>
-  <si>
-    <t>California Lawyers Association</t>
-  </si>
-  <si>
-    <t>https://calawyers.org/events/</t>
-  </si>
-  <si>
-    <t>Chicago Bar Association</t>
-  </si>
-  <si>
-    <t>https://www.chicagobar.org/events</t>
-  </si>
-  <si>
-    <t>International Association of Lawyers (UIA)</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>https://www.uianet.org/en/events</t>
-  </si>
-  <si>
-    <t>European Company Lawyers Association</t>
-  </si>
-  <si>
-    <t>Corporate Law</t>
-  </si>
-  <si>
-    <t>https://www.ecla.online/events</t>
-  </si>
-  <si>
-    <t>International Council on Commercial Arbitration Academy</t>
-  </si>
-  <si>
-    <t>Hong Kong International Arbitration Centre</t>
-  </si>
-  <si>
-    <t>https://www.hkiac.org/events</t>
-  </si>
-  <si>
-    <t>Dubai International Arbitration Centre</t>
-  </si>
-  <si>
-    <t>https://www.diac.ae/events</t>
-  </si>
-  <si>
-    <t>Financial Executives Networking Group</t>
-  </si>
-  <si>
-    <t>https://www.feng.org/events</t>
-  </si>
-  <si>
-    <t>Treasury Management Association of Singapore</t>
-  </si>
-  <si>
-    <t>https://www.tmas.org.sg/events</t>
-  </si>
-  <si>
-    <t>European Association of Corporate Treasurers</t>
-  </si>
-  <si>
-    <t>https://www.eact.eu/events</t>
-  </si>
-  <si>
-    <t>Investment Association</t>
-  </si>
-  <si>
-    <t>https://www.theia.org/events</t>
-  </si>
-  <si>
-    <t>Institutional Limited Partners Association</t>
-  </si>
-  <si>
-    <t>Private Equity</t>
-  </si>
-  <si>
-    <t>https://ilpa.org/events/</t>
-  </si>
-  <si>
-    <t>Invest Europe</t>
-  </si>
-  <si>
-    <t>Private Equity &amp; VC</t>
-  </si>
-  <si>
-    <t>https://www.investeurope.eu/events/</t>
-  </si>
-  <si>
-    <t>Private Equity CFO Association</t>
-  </si>
-  <si>
-    <t>https://www.privateequitycfo.com/events</t>
-  </si>
-  <si>
-    <t>Global Impact Investing Network (GIIN)</t>
-  </si>
-  <si>
-    <t>Impact Investing</t>
-  </si>
-  <si>
-    <t>https://thegiin.org/events/</t>
-  </si>
-  <si>
-    <t>FinTech Australia</t>
-  </si>
-  <si>
-    <t>https://www.fintechaustralia.org.au/events</t>
-  </si>
-  <si>
-    <t>Innovate Finance</t>
-  </si>
-  <si>
-    <t>https://www.innovatefinance.com/events/</t>
-  </si>
-  <si>
-    <t>Singapore FinTech Association</t>
-  </si>
-  <si>
-    <t>https://singaporefintech.org/events/</t>
-  </si>
-  <si>
-    <t>FinTech Association of Hong Kong</t>
-  </si>
-  <si>
-    <t>https://www.ftahk.org/events</t>
-  </si>
-  <si>
-    <t>Global Legal Entity Identifier Foundation (GLEIF)</t>
-  </si>
-  <si>
-    <t>Financial Infrastructure</t>
-  </si>
-  <si>
-    <t>https://www.gleif.org/en/events</t>
-  </si>
-  <si>
-    <t>International Association of Credit Rating Agencies</t>
-  </si>
-  <si>
-    <t>Credit Markets</t>
-  </si>
-  <si>
-    <t>https://www.iacra.org/events</t>
-  </si>
-  <si>
-    <t>Institute of Credit Management</t>
-  </si>
-  <si>
-    <t>Credit Management</t>
-  </si>
-  <si>
-    <t>https://www.cicm.com/events/</t>
-  </si>
-  <si>
-    <t>Credit Institute of Canada</t>
-  </si>
-  <si>
-    <t>https://creditedu.org/events</t>
-  </si>
-  <si>
-    <t>International Federation of Compliance Associations</t>
-  </si>
-  <si>
-    <t>https://www.ifca.org/events</t>
-  </si>
-  <si>
-    <t>Association of Governance, Risk &amp; Compliance (AGRC)</t>
-  </si>
-  <si>
-    <t>GRC</t>
-  </si>
-  <si>
-    <t>https://www.theagrc.org/events</t>
-  </si>
-  <si>
-    <t>Global Reporting Initiative (GRI)</t>
-  </si>
-  <si>
     <t>https://www.globalreporting.org/events/</t>
   </si>
   <si>
@@ -1859,15 +1804,6 @@
     <t>https://responsibleinvestment.org/events/</t>
   </si>
   <si>
-    <t>Institute of Business Ethics Asia</t>
-  </si>
-  <si>
-    <t>Business Ethics</t>
-  </si>
-  <si>
-    <t>Asia</t>
-  </si>
-  <si>
     <t>Association of Fraud Examiners UK Chapter</t>
   </si>
   <si>
@@ -1883,9 +1819,6 @@
     <t>https://www.iafe.org/events</t>
   </si>
   <si>
-    <t>Professional Risk Managers' International Association Asia</t>
-  </si>
-  <si>
     <t>Association of Certified Fraud Specialists</t>
   </si>
   <si>
@@ -1907,13 +1840,391 @@
     <t>https://www.ethicsboard.org/news-events</t>
   </si>
   <si>
-    <t>International Foundation for Ethics and Audit (Professional Forum)</t>
-  </si>
-  <si>
-    <t>Audit &amp; Ethics</t>
-  </si>
-  <si>
-    <t>https://cpeicai.org/#events</t>
+    <t>Insolvency and Bankruptcy Board of India (IBBI)</t>
+  </si>
+  <si>
+    <t>Insolvency, Finance &amp; Legal</t>
+  </si>
+  <si>
+    <t>https://ibbi.gov.in/search/index/events</t>
+  </si>
+  <si>
+    <t>National Institute of Public Finance and Policy (NIPFP)</t>
+  </si>
+  <si>
+    <t>Public Finance &amp; Tax</t>
+  </si>
+  <si>
+    <t>https://nipfp.org.in/event-index-page/</t>
+  </si>
+  <si>
+    <t>National Association of Enrolled Agents (NAEA)</t>
+  </si>
+  <si>
+    <t>https://www.naea.org/calendar/</t>
+  </si>
+  <si>
+    <t>Society of Actuaries (SOA)</t>
+  </si>
+  <si>
+    <t>Actuarial, Finance &amp; Risk</t>
+  </si>
+  <si>
+    <t>https://www.soa.org/prof-dev/events/</t>
+  </si>
+  <si>
+    <t>Public Risk Management Association (PRIMA)</t>
+  </si>
+  <si>
+    <t>Risk Management &amp; Finance</t>
+  </si>
+  <si>
+    <t>https://primacentral.org/resources/events/</t>
+  </si>
+  <si>
+    <t>USLAW NETWORK</t>
+  </si>
+  <si>
+    <t>https://www.uslaw.org/events/</t>
+  </si>
+  <si>
+    <t>National Society of Accountants (NSA)</t>
+  </si>
+  <si>
+    <t>https://nsawebinars.nsacct.org/upcoming-connected-webinars</t>
+  </si>
+  <si>
+    <t>National Society of Accountants for Cooperatives (NSAC)</t>
+  </si>
+  <si>
+    <t>Accounting, Tax &amp; Finance</t>
+  </si>
+  <si>
+    <t>https://nsacoop.org/events/</t>
+  </si>
+  <si>
+    <t>Illinois CPA Society (ICPAS)</t>
+  </si>
+  <si>
+    <t>https://www.icpas.org/</t>
+  </si>
+  <si>
+    <t>California Society of CPAs (CalCPA)</t>
+  </si>
+  <si>
+    <t>https://www.calcpa.org/</t>
+  </si>
+  <si>
+    <t>Florida Institute of CPAs (FICPA)</t>
+  </si>
+  <si>
+    <t>https://www.ficpa.org/cpe/conferences</t>
+  </si>
+  <si>
+    <t>Virginia Society of CPAs (VSCPA)</t>
+  </si>
+  <si>
+    <t>https://www.vscpa.com/event-sponsorship</t>
+  </si>
+  <si>
+    <t>Texas Society of CPAs (TXCPA)</t>
+  </si>
+  <si>
+    <t>https://www.tx.cpa/</t>
+  </si>
+  <si>
+    <t>Pennsylvania Institute of CPAs (PICPA)</t>
+  </si>
+  <si>
+    <t>Accounting &amp; Finance</t>
+  </si>
+  <si>
+    <t>https://www.picpa.org/cpe-events/featured-courses-events/annual-meeting</t>
+  </si>
+  <si>
+    <t>The Law Society of Singapore</t>
+  </si>
+  <si>
+    <t>https://www.lawsociety.org.sg/cpd-events/</t>
+  </si>
+  <si>
+    <t>Malaysian Bar Council - CPD</t>
+  </si>
+  <si>
+    <t>Legal &amp; Tax</t>
+  </si>
+  <si>
+    <t>https://cpd.malaysianbar.org.my/</t>
+  </si>
+  <si>
+    <t>Inland Revenue Board of Malaysia (HASiL)</t>
+  </si>
+  <si>
+    <t>https://www.hasil.gov.my/en/e-invoice/e-invoice-events/</t>
+  </si>
+  <si>
+    <t>Federal Tax Authority (FTA) UAE</t>
+  </si>
+  <si>
+    <t>https://tax.gov.ae/en/media.centre/events/events.aspx</t>
+  </si>
+  <si>
+    <t>Abu Dhabi Global Market (ADGM)</t>
+  </si>
+  <si>
+    <t>Finance, Legal &amp; Regulatory</t>
+  </si>
+  <si>
+    <t>https://www.adgm.com/events</t>
+  </si>
+  <si>
+    <t>Dubai International Financial Centre (DIFC)</t>
+  </si>
+  <si>
+    <t>https://www.difc.com/events</t>
+  </si>
+  <si>
+    <t>ICC UAE</t>
+  </si>
+  <si>
+    <t>Trade Finance &amp; Business</t>
+  </si>
+  <si>
+    <t>https://iccuae.ae/events-and-trainings/</t>
+  </si>
+  <si>
+    <t>Zakat, Tax and Customs Authority (ZATCA)</t>
+  </si>
+  <si>
+    <t>Tax &amp; Customs</t>
+  </si>
+  <si>
+    <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>https://zatca.gov.sa/en/MediaCenter/Events/Pages/RegisterLandingPage.aspx</t>
+  </si>
+  <si>
+    <t>LexisNexis Middle East</t>
+  </si>
+  <si>
+    <t>Qatar / Middle East</t>
+  </si>
+  <si>
+    <t>https://www.lexis.ae/events/</t>
+  </si>
+  <si>
+    <t>UNCTAD World Investment Forum</t>
+  </si>
+  <si>
+    <t>Investment &amp; Finance</t>
+  </si>
+  <si>
+    <t>Qatar / Global</t>
+  </si>
+  <si>
+    <t>https://worldinvestmentforum.unctad.org/</t>
+  </si>
+  <si>
+    <t>Risk Management Association (RMA)</t>
+  </si>
+  <si>
+    <t>Banking &amp; Finance</t>
+  </si>
+  <si>
+    <t>https://www.prosightfa.org/peer-sharing-collaboration/chapters/events/</t>
+  </si>
+  <si>
+    <t>Council of Financial Planners (COFP) India</t>
+  </si>
+  <si>
+    <t>Finance &amp; Tax</t>
+  </si>
+  <si>
+    <t>https://www.cofpindia.org/events</t>
+  </si>
+  <si>
+    <t>National Financial Reporting Authority (NFRA)</t>
+  </si>
+  <si>
+    <t>Accounting &amp; Audit</t>
+  </si>
+  <si>
+    <t>https://nfra.gov.in/nevents/</t>
+  </si>
+  <si>
+    <t>Foundation for International Taxation (FIT)</t>
+  </si>
+  <si>
+    <t>https://www.ffitindia.org/</t>
+  </si>
+  <si>
+    <t>Institute of Cost Accountants of India (ICMAI)</t>
+  </si>
+  <si>
+    <t>Accounting, Finance &amp; Tax</t>
+  </si>
+  <si>
+    <t>https://icmai.in/Home/Event/75</t>
+  </si>
+  <si>
+    <t>Indian Finance Association (IFA)</t>
+  </si>
+  <si>
+    <t>https://indiafa.org/conferences/</t>
+  </si>
+  <si>
+    <t>Supreme Audit Institution of India (SAI India)</t>
+  </si>
+  <si>
+    <t>Public Finance &amp; Audit</t>
+  </si>
+  <si>
+    <t>https://saiindia.gov.in/</t>
+  </si>
+  <si>
+    <t>Institute of Actuaries of India (IAI)</t>
+  </si>
+  <si>
+    <t>Finance, Risk &amp; Actuarial</t>
+  </si>
+  <si>
+    <t>https://www.actuariesindia.org/events-past</t>
+  </si>
+  <si>
+    <t>Indian Institute of Banking &amp; Finance (IIBF)</t>
+  </si>
+  <si>
+    <t>https://www.iibf.org.in/</t>
+  </si>
+  <si>
+    <t>Institute of International Bankers (IIB)</t>
+  </si>
+  <si>
+    <t>Banking &amp; Tax</t>
+  </si>
+  <si>
+    <t>https://www.iib.org/events/</t>
+  </si>
+  <si>
+    <t>Texas Association of Assessing Officers (TAAO)</t>
+  </si>
+  <si>
+    <t>Property Tax</t>
+  </si>
+  <si>
+    <t>https://www.taao.org/Conference/</t>
+  </si>
+  <si>
+    <t>Association for Financial Professionals (AFP)</t>
+  </si>
+  <si>
+    <t>Finance &amp; Treasury</t>
+  </si>
+  <si>
+    <t>https://www.financialprofessionals.org/events</t>
+  </si>
+  <si>
+    <t>Financial Planning Association (FPA)</t>
+  </si>
+  <si>
+    <t>Financial Planning</t>
+  </si>
+  <si>
+    <t>https://www.financialplanningassociation.org/learning/events</t>
+  </si>
+  <si>
+    <t>PayrollOrg</t>
+  </si>
+  <si>
+    <t>Payroll &amp; Tax</t>
+  </si>
+  <si>
+    <t>https://payroll.org/chapters/chapter-events</t>
+  </si>
+  <si>
+    <t>National Association of State Boards of Accountancy (NASBA)</t>
+  </si>
+  <si>
+    <t>https://nasba.org/meetings-events/</t>
+  </si>
+  <si>
+    <t>Institute of Singapore Chartered Accountants (ISCA)</t>
+  </si>
+  <si>
+    <t>https://isca.org.sg/member-support/events</t>
+  </si>
+  <si>
+    <t>Singapore Business Federation (SBF)</t>
+  </si>
+  <si>
+    <t>Business, Finance &amp; Trade</t>
+  </si>
+  <si>
+    <t>https://www.sbf.org.sg/events</t>
+  </si>
+  <si>
+    <t>Tax Academy of Singapore</t>
+  </si>
+  <si>
+    <t>https://www.taxacademy.sg/seminars-and-conferences/</t>
+  </si>
+  <si>
+    <t>Institute of Banking and Finance Singapore (IBF)</t>
+  </si>
+  <si>
+    <t>https://www.ibf.org.sg/home/events</t>
+  </si>
+  <si>
+    <t>International Fiscal Association Malaysia (IFA Malaysia)</t>
+  </si>
+  <si>
+    <t>https://www.ifa.my/eventshome</t>
+  </si>
+  <si>
+    <t>Chartered Tax Institute of Malaysia (CTIM)</t>
+  </si>
+  <si>
+    <t>https://www.ctim.org.my/events/</t>
+  </si>
+  <si>
+    <t>Malaysian Institute of Accountants (MIA)</t>
+  </si>
+  <si>
+    <t>https://mia.org.my/events/</t>
+  </si>
+  <si>
+    <t>Malaysian Accounting Firms Association (MAFA)</t>
+  </si>
+  <si>
+    <t>https://mafa.org.my/events/</t>
+  </si>
+  <si>
+    <t>Taxation Society UAE</t>
+  </si>
+  <si>
+    <t>Tax &amp; Compliance</t>
+  </si>
+  <si>
+    <t>https://taxationsociety.org/events-conferences/</t>
+  </si>
+  <si>
+    <t>Union of Arab Banks (UAB)</t>
+  </si>
+  <si>
+    <t>Middle East</t>
+  </si>
+  <si>
+    <t>https://uabonline.org/event/</t>
+  </si>
+  <si>
+    <t>Bahrain Institute of Banking and Finance (BIBF)</t>
+  </si>
+  <si>
+    <t>Bahrain</t>
+  </si>
+  <si>
+    <t>https://www.bibf.com/events/</t>
   </si>
 </sst>
 </file>
@@ -2285,7 +2596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E287"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -2326,7 +2637,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>625</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2334,16 +2645,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2351,16 +2662,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2368,16 +2679,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2385,16 +2696,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2402,16 +2713,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2419,16 +2730,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -2436,16 +2747,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -2453,16 +2764,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -2470,16 +2781,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -2487,16 +2798,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -2504,16 +2815,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -2521,16 +2832,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -2538,16 +2849,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -2555,16 +2866,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -2572,16 +2883,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -2589,16 +2900,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -2606,16 +2917,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -2623,16 +2934,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -2640,16 +2951,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -2657,16 +2968,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -2674,16 +2985,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -2691,16 +3002,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -2708,16 +3019,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -2725,16 +3036,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -2742,16 +3053,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -2759,16 +3070,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -2776,16 +3087,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -2793,16 +3104,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -2810,16 +3121,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -2827,16 +3138,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -2844,16 +3155,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -2861,16 +3172,16 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -2878,16 +3189,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -2895,16 +3206,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2912,16 +3223,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -2929,16 +3240,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -2946,16 +3257,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2963,16 +3274,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2980,16 +3291,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2997,16 +3308,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -3014,16 +3325,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D43" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -3031,16 +3342,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -3048,16 +3359,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C45" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -3065,16 +3376,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -3082,16 +3393,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -3099,16 +3410,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -3116,16 +3427,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -3133,16 +3444,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -3150,16 +3461,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -3167,16 +3478,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D52" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -3184,16 +3495,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -3201,16 +3512,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C54" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D54" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -3218,16 +3529,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C55" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -3235,16 +3546,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -3252,16 +3563,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C57" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -3269,16 +3580,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -3286,16 +3597,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C59" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -3303,16 +3614,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -3320,16 +3631,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C61" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D61" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -3337,16 +3648,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C62" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D62" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -3354,16 +3665,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -3371,16 +3682,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C64" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D64" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -3388,16 +3699,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D65" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -3405,16 +3716,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C66" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D66" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -3422,16 +3733,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C67" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D67" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -3439,16 +3750,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C68" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D68" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -3456,16 +3767,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C69" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -3473,16 +3784,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C70" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D70" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -3490,16 +3801,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C71" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D71" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -3507,16 +3818,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C72" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D72" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -3524,16 +3835,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C73" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D73" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -3541,16 +3852,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C74" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D74" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -3558,16 +3869,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C75" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D75" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -3575,16 +3886,16 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C76" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D76" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -3592,16 +3903,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C77" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D77" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -3609,16 +3920,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C78" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D78" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -3626,16 +3937,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C79" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D79" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -3643,16 +3954,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C80" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D80" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -3660,16 +3971,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C81" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D81" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -3677,16 +3988,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C82" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D82" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -3694,16 +4005,16 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C83" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D83" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -3711,16 +4022,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C84" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D84" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -3728,16 +4039,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C85" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D85" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -3745,16 +4056,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C86" t="s">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="D86" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -3762,16 +4073,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C87" t="s">
-        <v>19</v>
+        <v>226</v>
       </c>
       <c r="D87" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -3779,16 +4090,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C88" t="s">
-        <v>227</v>
+        <v>64</v>
       </c>
       <c r="D88" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -3796,16 +4107,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C89" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D89" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -3813,16 +4124,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C90" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D90" t="s">
-        <v>56</v>
+        <v>233</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -3830,16 +4141,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>235</v>
+      </c>
+      <c r="C91" t="s">
+        <v>64</v>
+      </c>
+      <c r="D91" t="s">
         <v>233</v>
       </c>
-      <c r="C91" t="s">
-        <v>19</v>
-      </c>
-      <c r="D91" t="s">
-        <v>234</v>
-      </c>
       <c r="E91" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -3847,16 +4158,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C92" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>234</v>
+        <v>57</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -3864,16 +4175,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C93" t="s">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="D93" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -3881,16 +4192,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C94" t="s">
-        <v>241</v>
+        <v>84</v>
       </c>
       <c r="D94" t="s">
-        <v>184</v>
+        <v>26</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -3898,16 +4209,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C95" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D95" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -3915,16 +4226,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C96" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="D96" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -3932,16 +4243,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C97" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="D97" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -3949,16 +4260,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C98" t="s">
-        <v>63</v>
+        <v>251</v>
       </c>
       <c r="D98" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -3966,16 +4277,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C99" t="s">
-        <v>252</v>
+        <v>91</v>
       </c>
       <c r="D99" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -3983,118 +4294,118 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C100" t="s">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D100" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A101" s="3">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
-        <v>256</v>
-      </c>
-      <c r="C101" t="s">
-        <v>9</v>
-      </c>
-      <c r="D101" t="s">
-        <v>37</v>
-      </c>
-      <c r="E101" s="2" t="s">
+      <c r="B101" s="3" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C101" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>187</v>
+        <v>38</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>101</v>
+        <v>273</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -4102,135 +4413,135 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>271</v>
+        <v>111</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>274</v>
+        <v>111</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>110</v>
+        <v>191</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>206</v>
+        <v>26</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>206</v>
+        <v>26</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>190</v>
+        <v>286</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>190</v>
+        <v>289</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -4238,16 +4549,16 @@
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -4255,135 +4566,135 @@
         <v>115</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>116</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>117</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>299</v>
+        <v>174</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>299</v>
+        <v>174</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>150</v>
+        <v>207</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>119</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>304</v>
+        <v>174</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>7</v>
+        <v>307</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>121</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>173</v>
+        <v>312</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>122</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>173</v>
+        <v>10</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>311</v>
+        <v>233</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
@@ -4391,84 +4702,84 @@
         <v>123</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>173</v>
+        <v>317</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>124</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>316</v>
+        <v>10</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>56</v>
+        <v>307</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>125</v>
       </c>
       <c r="B126" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C126" s="3" t="s">
-        <v>318</v>
-      </c>
       <c r="D126" s="3" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>126</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>30</v>
+        <v>324</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>127</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>9</v>
+        <v>327</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>234</v>
+        <v>38</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
@@ -4476,135 +4787,135 @@
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>324</v>
+        <v>64</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>129</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>311</v>
+        <v>38</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>130</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>324</v>
+        <v>64</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>131</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>331</v>
+        <v>64</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>311</v>
+        <v>38</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>132</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>42</v>
+        <v>233</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>133</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>334</v>
+        <v>64</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>134</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>135</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>63</v>
+        <v>345</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
@@ -4612,16 +4923,16 @@
         <v>136</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
@@ -4629,118 +4940,118 @@
         <v>137</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>138</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>139</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>140</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>63</v>
+        <v>356</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>141</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>142</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>143</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>110</v>
+        <v>363</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>188</v>
+        <v>38</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
@@ -4748,135 +5059,135 @@
         <v>144</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>110</v>
+        <v>363</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>145</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>110</v>
+        <v>368</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>146</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>110</v>
+        <v>363</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>37</v>
+        <v>371</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>147</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>124</v>
+        <v>363</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>234</v>
+        <v>23</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>148</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>149</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>25</v>
+        <v>378</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>150</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>42</v>
+        <v>381</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>151</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>375</v>
+        <v>384</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
@@ -4884,118 +5195,118 @@
         <v>152</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E153" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>387</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>153</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>390</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>154</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>155</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>156</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>150</v>
+        <v>43</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>157</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>158</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
@@ -5003,16 +5314,16 @@
         <v>159</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>395</v>
+        <v>38</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
@@ -5020,305 +5331,305 @@
         <v>160</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>398</v>
+        <v>23</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>161</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>355</v>
+        <v>402</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>162</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>382</v>
+        <v>188</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>163</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>164</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>165</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>382</v>
+        <v>57</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>166</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>401</v>
+        <v>57</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>167</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A169" s="3">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A169" s="4">
         <v>168</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A170" s="3">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="4">
         <v>169</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>389</v>
+        <v>57</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A171" s="3">
+      <c r="A171" s="4">
         <v>170</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>187</v>
+        <v>57</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A172" s="3">
+      <c r="A172" s="4">
         <v>171</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>427</v>
+        <v>261</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A173" s="3">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="4">
         <v>172</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A174" s="3">
+      <c r="A174" s="4">
         <v>173</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>56</v>
+        <v>207</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A175" s="3">
+      <c r="A175" s="4">
         <v>174</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A176" s="3">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="4">
         <v>175</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>176</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>177</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
@@ -5326,16 +5637,16 @@
         <v>178</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
@@ -5343,33 +5654,33 @@
         <v>179</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>262</v>
+        <v>462</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>180</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
@@ -5377,16 +5688,16 @@
         <v>181</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
@@ -5394,16 +5705,16 @@
         <v>182</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>37</v>
+        <v>188</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
@@ -5411,67 +5722,67 @@
         <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>184</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
         <v>185</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>186</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
@@ -5479,16 +5790,16 @@
         <v>187</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
@@ -5496,50 +5807,50 @@
         <v>188</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>189</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>190</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>260</v>
+        <v>495</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
@@ -5547,67 +5858,67 @@
         <v>191</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>484</v>
+        <v>10</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>192</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>487</v>
+        <v>10</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>56</v>
+        <v>378</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>193</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>490</v>
+        <v>10</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
@@ -5615,33 +5926,33 @@
         <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>316</v>
+        <v>10</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>196</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
@@ -5649,101 +5960,101 @@
         <v>197</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>198</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>37</v>
+        <v>233</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>199</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>505</v>
+        <v>206</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>200</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>508</v>
+        <v>206</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>201</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>147</v>
+        <v>378</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>202</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>389</v>
+        <v>151</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
@@ -5751,16 +6062,16 @@
         <v>203</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
@@ -5768,16 +6079,16 @@
         <v>204</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>517</v>
+        <v>46</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
@@ -5785,16 +6096,16 @@
         <v>205</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
@@ -5802,16 +6113,16 @@
         <v>206</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>522</v>
+        <v>46</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>150</v>
+        <v>530</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
@@ -5819,33 +6130,33 @@
         <v>207</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>56</v>
+        <v>233</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>208</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>525</v>
+        <v>356</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>234</v>
+        <v>148</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
@@ -5853,16 +6164,16 @@
         <v>209</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>205</v>
+        <v>356</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>56</v>
+        <v>387</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
@@ -5870,50 +6181,50 @@
         <v>210</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>205</v>
+        <v>64</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>211</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>389</v>
+        <v>43</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>212</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>150</v>
+        <v>233</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
@@ -5921,16 +6232,16 @@
         <v>213</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>45</v>
+        <v>289</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
@@ -5938,16 +6249,16 @@
         <v>214</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>45</v>
+        <v>548</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
@@ -5955,16 +6266,16 @@
         <v>215</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>45</v>
+        <v>551</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>37</v>
+        <v>233</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
@@ -5972,16 +6283,16 @@
         <v>216</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>45</v>
+        <v>548</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>544</v>
+        <v>38</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
@@ -5989,33 +6300,33 @@
         <v>217</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>234</v>
+        <v>38</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>218</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>367</v>
+        <v>459</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>368</v>
+        <v>559</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
@@ -6023,16 +6334,16 @@
         <v>219</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>367</v>
+        <v>459</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
@@ -6040,16 +6351,16 @@
         <v>220</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>367</v>
+        <v>459</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>398</v>
+        <v>43</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
@@ -6057,50 +6368,50 @@
         <v>221</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>63</v>
+        <v>459</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>37</v>
+        <v>148</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>222</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>83</v>
+        <v>567</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>223</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>83</v>
+        <v>570</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>234</v>
+        <v>57</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
@@ -6108,16 +6419,16 @@
         <v>224</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>293</v>
+        <v>573</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
@@ -6125,50 +6436,50 @@
         <v>225</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
         <v>226</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>566</v>
+        <v>91</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>234</v>
+        <v>57</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A228" s="4">
         <v>227</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
@@ -6176,16 +6487,16 @@
         <v>228</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
@@ -6193,16 +6504,16 @@
         <v>229</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>470</v>
+        <v>586</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>574</v>
+        <v>587</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
@@ -6210,33 +6521,33 @@
         <v>230</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>470</v>
+        <v>583</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>231</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>470</v>
+        <v>591</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
@@ -6244,50 +6555,50 @@
         <v>232</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>470</v>
+        <v>171</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>233</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>234</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>585</v>
+        <v>171</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>586</v>
+        <v>599</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
@@ -6295,50 +6606,50 @@
         <v>235</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>587</v>
+        <v>600</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>588</v>
+        <v>81</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>236</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>237</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>90</v>
+        <v>606</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>593</v>
+        <v>607</v>
       </c>
     </row>
     <row r="239" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -6346,33 +6657,33 @@
         <v>238</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>239</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>220</v>
+        <v>10</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
@@ -6380,50 +6691,50 @@
         <v>240</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>241</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>220</v>
+        <v>617</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>242</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>605</v>
+        <v>46</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>606</v>
+        <v>620</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
@@ -6431,67 +6742,67 @@
         <v>243</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>608</v>
+        <v>6</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>609</v>
+        <v>38</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>244</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>610</v>
+        <v>623</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>170</v>
+        <v>624</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>245</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>246</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>615</v>
+        <v>628</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>609</v>
+        <v>38</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>86</v>
+        <v>629</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
@@ -6499,71 +6810,683 @@
         <v>247</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>616</v>
+        <v>630</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>248</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>618</v>
+        <v>632</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>249</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>620</v>
+        <v>634</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>250</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>623</v>
+        <v>636</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>624</v>
+        <v>637</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>209</v>
+        <v>638</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A252" s="4">
+        <v>251</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A253" s="4">
+        <v>252</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A254" s="4">
+        <v>253</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A255" s="4">
+        <v>254</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A256" s="4">
+        <v>255</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A257" s="4">
+        <v>256</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A258" s="4">
+        <v>257</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A259" s="4">
+        <v>258</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A260" s="4">
+        <v>259</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A261" s="4">
+        <v>260</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A262" s="4">
+        <v>261</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A263" s="4">
+        <v>262</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A264" s="4">
+        <v>263</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A265" s="4">
+        <v>264</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A266" s="4">
+        <v>265</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A267" s="4">
+        <v>266</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A268" s="4">
+        <v>267</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A269" s="4">
+        <v>268</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A270" s="4">
+        <v>269</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A271" s="4">
+        <v>270</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A272" s="4">
+        <v>271</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A273" s="4">
+        <v>272</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A274" s="4">
+        <v>273</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A275" s="4">
+        <v>274</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A276" s="4">
+        <v>275</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A277" s="4">
+        <v>276</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A278" s="4">
+        <v>277</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A279" s="4">
+        <v>278</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A280" s="4">
+        <v>279</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A281" s="4">
+        <v>280</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A282" s="4">
+        <v>281</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A283" s="4">
+        <v>282</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A284" s="4">
+        <v>283</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="C284" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A285" s="4">
+        <v>284</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A286" s="4">
+        <v>285</v>
+      </c>
+      <c r="B286" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="C286" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A287" s="4">
+        <v>286</v>
+      </c>
+      <c r="B287" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>733</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E251" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E250" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" location="events" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="E3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -6648,170 +7571,195 @@
     <hyperlink ref="E82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
     <hyperlink ref="E83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
     <hyperlink ref="E84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="E85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="E86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="E87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="E88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="E89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="E90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="E91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="E92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="E93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="E94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="E95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="E96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="E97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="E98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="E99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="E100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="E101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="E102" r:id="rId101" xr:uid="{5C40277A-CD42-409B-9795-DE639675431B}"/>
-    <hyperlink ref="E103" r:id="rId102" xr:uid="{95F9CCAB-326C-41EA-AE92-2F28D82E7CC0}"/>
-    <hyperlink ref="E104" r:id="rId103" xr:uid="{3C5651C0-91EA-41E4-8605-583F97198357}"/>
-    <hyperlink ref="E105" r:id="rId104" xr:uid="{50433251-5191-4C13-8C47-EA60A378C553}"/>
-    <hyperlink ref="E106" r:id="rId105" xr:uid="{ECCFB81D-3D03-4EA2-B620-1942B96C8ECA}"/>
-    <hyperlink ref="E107" r:id="rId106" xr:uid="{2C13FC0A-8CEC-4039-A04F-95B83D744143}"/>
-    <hyperlink ref="E108" r:id="rId107" xr:uid="{52E5BAF7-A7F1-494F-9F4F-FA24A04150BA}"/>
-    <hyperlink ref="E109" r:id="rId108" xr:uid="{E97AE6C3-231F-4A53-BC7D-1185F476DAAF}"/>
-    <hyperlink ref="E110" r:id="rId109" xr:uid="{422D6C91-CA51-4164-BED9-8ED3C786AE05}"/>
-    <hyperlink ref="E111" r:id="rId110" xr:uid="{B735D064-C28D-4C5C-966C-6E5A8888C3AA}"/>
-    <hyperlink ref="E112" r:id="rId111" xr:uid="{16E56524-4C55-49F4-B301-9769BB24A43E}"/>
-    <hyperlink ref="E113" r:id="rId112" xr:uid="{3ABE7AC8-8932-4C4E-9B2E-B4F74B1D54F6}"/>
-    <hyperlink ref="E114" r:id="rId113" xr:uid="{E4C44CE8-D590-4075-9D46-BB34AACC25EC}"/>
-    <hyperlink ref="E115" r:id="rId114" xr:uid="{F27FCF4A-E741-434D-8A57-ECD405A4F109}"/>
-    <hyperlink ref="E116" r:id="rId115" xr:uid="{2716493C-3704-475C-AC95-997689EB8500}"/>
-    <hyperlink ref="E117" r:id="rId116" xr:uid="{2DBB01F8-380D-4966-8ED8-6CF13209CBD8}"/>
-    <hyperlink ref="E118" r:id="rId117" xr:uid="{C67B7D61-672D-4A9B-8979-943EDE92633E}"/>
-    <hyperlink ref="E119" r:id="rId118" xr:uid="{E59D4C7D-6ED3-42B6-A513-48D71304F0BD}"/>
-    <hyperlink ref="E120" r:id="rId119" xr:uid="{5C7BDF52-BDC3-46C0-8241-819231239D1B}"/>
-    <hyperlink ref="E121" r:id="rId120" xr:uid="{4CC39688-30CB-42C2-AB12-E41020F3ECCE}"/>
-    <hyperlink ref="E122" r:id="rId121" xr:uid="{C6AA2EC6-67B3-427B-8B02-77E63F354278}"/>
-    <hyperlink ref="E123" r:id="rId122" xr:uid="{D6C8D572-AA5B-4C40-844E-43233E615B0B}"/>
-    <hyperlink ref="E124" r:id="rId123" xr:uid="{A17EC795-BE16-4D98-95C9-3E452636458B}"/>
-    <hyperlink ref="E125" r:id="rId124" xr:uid="{C6C76BB8-C064-48FD-A136-99E93100F2F8}"/>
-    <hyperlink ref="E126" r:id="rId125" xr:uid="{0BA90AE4-C26D-4202-8769-67051862EDE4}"/>
-    <hyperlink ref="E127" r:id="rId126" xr:uid="{75EA91A7-E79F-4B1D-99D3-E2FE8DC08769}"/>
-    <hyperlink ref="E128" r:id="rId127" xr:uid="{089A3223-6167-4F24-A3DF-0C352E4F370E}"/>
-    <hyperlink ref="E129" r:id="rId128" xr:uid="{4ADE88C6-FAFD-438F-BEDE-3A666A2D72F9}"/>
-    <hyperlink ref="E130" r:id="rId129" xr:uid="{DEB89992-D31E-488D-87E9-6D74642E5773}"/>
-    <hyperlink ref="E131" r:id="rId130" xr:uid="{3B59F6F3-3D81-4B96-9DE1-6E5BF7190B18}"/>
-    <hyperlink ref="E132" r:id="rId131" xr:uid="{F37C6302-BABE-458F-9E1A-90E030D070B4}"/>
-    <hyperlink ref="E133" r:id="rId132" xr:uid="{6D693DBD-841B-476B-A825-32952C24DEF3}"/>
-    <hyperlink ref="E134" r:id="rId133" xr:uid="{75541D52-DF70-4B4A-9516-274D712EC29B}"/>
-    <hyperlink ref="E135" r:id="rId134" xr:uid="{F3B44C0F-ACF2-4193-AB4E-13F16517A5E7}"/>
-    <hyperlink ref="E136" r:id="rId135" xr:uid="{8C59AE21-DA37-45AD-A722-A6767D93C190}"/>
-    <hyperlink ref="E137" r:id="rId136" xr:uid="{50403EF4-00D1-4F2C-AEE9-4F0A8A560EA2}"/>
-    <hyperlink ref="E138" r:id="rId137" xr:uid="{2D6D36DB-CDCA-4DAA-AA35-FCD9ABFAC108}"/>
-    <hyperlink ref="E139" r:id="rId138" xr:uid="{02B19F46-0DF8-475E-9736-1CA6C469669E}"/>
-    <hyperlink ref="E140" r:id="rId139" xr:uid="{D0DEFEFD-7244-4745-8EF3-326BA1A2CCB3}"/>
-    <hyperlink ref="E141" r:id="rId140" xr:uid="{A410539D-9020-463F-8FA8-3B64130B9F06}"/>
-    <hyperlink ref="E142" r:id="rId141" xr:uid="{6FF8E1EB-613C-4007-A1FD-5E1EBACD7559}"/>
-    <hyperlink ref="E143" r:id="rId142" xr:uid="{7380C72D-5466-4CAF-85A1-BC769455A84D}"/>
-    <hyperlink ref="E144" r:id="rId143" xr:uid="{76BF7A67-5FF0-43DD-9E5C-267A6148B8DC}"/>
-    <hyperlink ref="E145" r:id="rId144" xr:uid="{B26064E1-A375-47D3-8EA6-EF58C3AC9F28}"/>
-    <hyperlink ref="E146" r:id="rId145" xr:uid="{67319177-F4FE-4002-97E2-DDE25C2BAE19}"/>
-    <hyperlink ref="E147" r:id="rId146" xr:uid="{E058EBF6-1F28-4129-9183-5633436EAD0C}"/>
-    <hyperlink ref="E148" r:id="rId147" xr:uid="{21260E74-9FBB-4C85-8B02-F4C245C33657}"/>
-    <hyperlink ref="E149" r:id="rId148" xr:uid="{DBCB992E-1B49-4E6B-B7C1-F92635DCDEB4}"/>
-    <hyperlink ref="E150" r:id="rId149" xr:uid="{352A2FF1-3CF2-473E-B649-84D39BE1DCCE}"/>
-    <hyperlink ref="E151" r:id="rId150" xr:uid="{2DA75D5A-BAC6-4581-97F9-6F49D170F5BB}"/>
-    <hyperlink ref="E155" r:id="rId151" xr:uid="{09F4F8D6-9678-4486-BDBA-668D1C804ABF}"/>
-    <hyperlink ref="E156" r:id="rId152" xr:uid="{BD83A62D-CB7B-488F-BBE5-C6F703594358}"/>
-    <hyperlink ref="E157" r:id="rId153" xr:uid="{3B99AC6D-B824-44A9-BC09-F3522B65E210}"/>
-    <hyperlink ref="E158" r:id="rId154" xr:uid="{9CA6974C-3CD7-44A0-99C2-F4A41C029A31}"/>
-    <hyperlink ref="E159" r:id="rId155" xr:uid="{343ADF4F-6288-4B09-AF71-CCAE4FACC83A}"/>
-    <hyperlink ref="E160" r:id="rId156" xr:uid="{8C87603A-52F4-417A-8114-84833E52E7FA}"/>
-    <hyperlink ref="E161" r:id="rId157" xr:uid="{D7C25060-F026-4D4C-9532-5A74E3A89D24}"/>
-    <hyperlink ref="E162" r:id="rId158" xr:uid="{D0E03640-CF56-4CDC-B996-816A5F9D41CA}"/>
-    <hyperlink ref="E163" r:id="rId159" xr:uid="{E31C17C3-5C84-41CF-A259-7B120BA8E4E8}"/>
-    <hyperlink ref="E164" r:id="rId160" xr:uid="{092FD797-4FC1-4436-9DFC-010D94B032A7}"/>
-    <hyperlink ref="E165" r:id="rId161" xr:uid="{8E0EB030-2A12-49F8-AE05-8A2AED583359}"/>
-    <hyperlink ref="E166" r:id="rId162" xr:uid="{5C4E1409-4E37-450B-9FF6-7FDB1FAE0960}"/>
-    <hyperlink ref="E167" r:id="rId163" xr:uid="{F8E9A109-2DB4-4BAD-B46D-6909E22D77F5}"/>
-    <hyperlink ref="E168" r:id="rId164" xr:uid="{8A55D65A-FECD-4A86-826D-161E19082867}"/>
-    <hyperlink ref="E169" r:id="rId165" xr:uid="{C30C1F84-80D4-4396-883A-676CC7405030}"/>
-    <hyperlink ref="E170" r:id="rId166" xr:uid="{90D5F9DB-0CEE-4C35-AB1F-BD059EA205CA}"/>
-    <hyperlink ref="E171" r:id="rId167" xr:uid="{4125A64B-E3BC-4C65-9AB5-C878A8CD38A9}"/>
-    <hyperlink ref="E172" r:id="rId168" xr:uid="{7BF8CEA7-5299-4E01-9BCC-102AD2E7D41E}"/>
-    <hyperlink ref="E173" r:id="rId169" xr:uid="{30E15B50-7AED-4F6B-9386-6B9A7778D162}"/>
-    <hyperlink ref="E174" r:id="rId170" xr:uid="{F42F5C1E-1B81-4FDD-9864-17DB93BC07D4}"/>
-    <hyperlink ref="E175" r:id="rId171" xr:uid="{A23EF7DA-CF0E-4408-92EC-A3225548EB76}"/>
-    <hyperlink ref="E176" r:id="rId172" xr:uid="{0E001239-2A29-4667-879C-A1EED1E0864A}"/>
-    <hyperlink ref="E177" r:id="rId173" xr:uid="{F05E45A1-5936-426C-B665-B48E3493EAC2}"/>
-    <hyperlink ref="E178" r:id="rId174" xr:uid="{E933AD7B-5F8D-48A7-B146-938BBFFB3C90}"/>
-    <hyperlink ref="E179" r:id="rId175" xr:uid="{2A349ACF-26AF-4E30-B821-BE7C3EF494E4}"/>
-    <hyperlink ref="E180" r:id="rId176" xr:uid="{24B345D5-2FCE-4D0F-B9D8-71D2D400DAEC}"/>
-    <hyperlink ref="E181" r:id="rId177" xr:uid="{DA3A91E1-E03D-42D8-B661-A12C5F65DC76}"/>
-    <hyperlink ref="E182" r:id="rId178" xr:uid="{0A3CAAF7-CB9B-4045-A036-61F910EC2ED6}"/>
-    <hyperlink ref="E183" r:id="rId179" xr:uid="{F403625D-7E5D-4358-A165-0626F615B16E}"/>
-    <hyperlink ref="E184" r:id="rId180" xr:uid="{FBE12B36-0657-40EF-91F1-5D8D4A547F0F}"/>
-    <hyperlink ref="E185" r:id="rId181" xr:uid="{682ED47E-B3C0-4D4A-9F52-EDEE98F4636A}"/>
-    <hyperlink ref="E186" r:id="rId182" xr:uid="{9A56E22C-617E-431E-A2AC-BA8D58982AFA}"/>
-    <hyperlink ref="E187" r:id="rId183" xr:uid="{E8B4CD3B-BC44-45CE-979A-536FAB6EEA12}"/>
-    <hyperlink ref="E188" r:id="rId184" xr:uid="{56208164-5FC0-411A-99C7-ABE3FEBE89FF}"/>
-    <hyperlink ref="E189" r:id="rId185" xr:uid="{04D3767E-B8B9-48A4-84FC-3ECFAB336C16}"/>
-    <hyperlink ref="E190" r:id="rId186" xr:uid="{B544528C-AEA6-4475-9F64-1EB8A1BFFAE6}"/>
-    <hyperlink ref="E191" r:id="rId187" xr:uid="{32B0CDA1-5CBC-479D-A24E-49D69FAB4ADA}"/>
-    <hyperlink ref="E192" r:id="rId188" xr:uid="{852BD169-0FBF-4D0D-9C26-0563794E2E89}"/>
-    <hyperlink ref="E193" r:id="rId189" xr:uid="{4AD2986D-C97A-4161-A3C3-4E69807F80A6}"/>
-    <hyperlink ref="E194" r:id="rId190" xr:uid="{56770834-BC59-4653-95EA-036C0376713D}"/>
-    <hyperlink ref="E195" r:id="rId191" xr:uid="{AD4C4E54-93B4-4F53-92DA-A5647E539FA7}"/>
-    <hyperlink ref="E196" r:id="rId192" xr:uid="{6BAB425F-0B30-4A11-98B3-F54E03FF46F9}"/>
-    <hyperlink ref="E197" r:id="rId193" xr:uid="{8C1C7996-8666-44B6-8571-52D4A0E1BB8B}"/>
-    <hyperlink ref="E198" r:id="rId194" xr:uid="{9080835F-4D15-48AE-9995-475815E4E869}"/>
-    <hyperlink ref="E199" r:id="rId195" xr:uid="{03173FF6-F7F1-415C-ABAC-BE9D0C650F84}"/>
-    <hyperlink ref="E200" r:id="rId196" xr:uid="{44D878EC-2E6C-4564-8966-AC9020AB6C7A}"/>
-    <hyperlink ref="E201" r:id="rId197" xr:uid="{05E4FF16-5B1D-4F52-B73F-30D9D46C14DC}"/>
-    <hyperlink ref="E202" r:id="rId198" xr:uid="{CD5F1D91-99B2-4029-A6A3-0610C5444CA5}"/>
-    <hyperlink ref="E203" r:id="rId199" xr:uid="{CD2D68A9-D7F3-459C-BA47-08AF99E5DE5F}"/>
-    <hyperlink ref="E204" r:id="rId200" xr:uid="{C4F0213D-D005-492F-A4EA-C6BF5203DA34}"/>
-    <hyperlink ref="E205" r:id="rId201" xr:uid="{959779A7-1D68-48AA-A32D-9E5FEBE402F1}"/>
-    <hyperlink ref="E206" r:id="rId202" xr:uid="{71F23FF3-11DE-4F38-8D2F-EBF9B79C1C32}"/>
-    <hyperlink ref="E207" r:id="rId203" xr:uid="{E3440C46-BAA2-438D-99BA-A5E1A3806662}"/>
-    <hyperlink ref="E208" r:id="rId204" xr:uid="{CD6745AF-393E-4D52-9F6A-7F5990EC04E3}"/>
-    <hyperlink ref="E209" r:id="rId205" xr:uid="{E63366D6-B6BE-4051-9DB4-A7B7DB5131A3}"/>
-    <hyperlink ref="E210" r:id="rId206" xr:uid="{EC403F05-C612-491C-A23F-74EEDD813359}"/>
-    <hyperlink ref="E211" r:id="rId207" xr:uid="{75F435D3-1F7F-47A1-9135-A03ED9ADEE36}"/>
-    <hyperlink ref="E212" r:id="rId208" xr:uid="{FCD43F8E-F377-417C-8E6E-C0CEF1795C46}"/>
-    <hyperlink ref="E213" r:id="rId209" xr:uid="{A535029A-C9CA-47CB-B79D-1DAE859431B6}"/>
-    <hyperlink ref="E214" r:id="rId210" xr:uid="{4FA1A1DA-2646-4FCE-BBAF-C69676D26B38}"/>
-    <hyperlink ref="E215" r:id="rId211" xr:uid="{3A493B79-8144-41B8-835E-AC1992114948}"/>
-    <hyperlink ref="E216" r:id="rId212" xr:uid="{F5D35DFF-F3E5-4047-8098-667F172AE38C}"/>
-    <hyperlink ref="E217" r:id="rId213" xr:uid="{47CF76DA-7BDC-4504-A148-95D90A71A777}"/>
-    <hyperlink ref="E218" r:id="rId214" xr:uid="{02EA5A27-6D61-41A5-9DF0-49F464DF5C4A}"/>
-    <hyperlink ref="E219" r:id="rId215" xr:uid="{1ACE5E07-EEE3-4892-8B57-93270F2A2D20}"/>
-    <hyperlink ref="E220" r:id="rId216" xr:uid="{CED9EE54-66B7-4A02-945A-4C9AC1E8964B}"/>
-    <hyperlink ref="E221" r:id="rId217" xr:uid="{415385E6-37A4-4CFF-9417-9EEDFD87EB72}"/>
-    <hyperlink ref="E222" r:id="rId218" xr:uid="{473DAE52-ACA7-4DA7-99DC-A9551AD13D86}"/>
-    <hyperlink ref="E223" r:id="rId219" xr:uid="{3EF1AA55-A5F3-445D-B720-7120F5AC514C}"/>
-    <hyperlink ref="E224" r:id="rId220" xr:uid="{89D1DACE-2F40-4901-A023-42CE887268DC}"/>
-    <hyperlink ref="E225" r:id="rId221" xr:uid="{F29BF590-D7D0-4181-8EAE-E4C26DB2FA18}"/>
-    <hyperlink ref="E226" r:id="rId222" xr:uid="{86AB56A4-54A1-4BDC-A5C4-CC3A03C1A006}"/>
-    <hyperlink ref="E227" r:id="rId223" xr:uid="{85395985-4005-482F-A413-BA3A9F1243BA}"/>
-    <hyperlink ref="E228" r:id="rId224" xr:uid="{704982EE-2FEB-41F6-B644-BAD29F7284B9}"/>
-    <hyperlink ref="E229" r:id="rId225" xr:uid="{345557E5-C8DC-4191-9A77-64D5BB7EE5E8}"/>
-    <hyperlink ref="E230" r:id="rId226" xr:uid="{F5AE550E-756F-4F1C-A562-45BB07ADDFDE}"/>
-    <hyperlink ref="E231" r:id="rId227" xr:uid="{F2D8F2C0-CD12-400A-BEAA-2D336F1971F9}"/>
-    <hyperlink ref="E232" r:id="rId228" xr:uid="{4C25E222-1C0B-47C1-BC5B-D1E9AACDFE35}"/>
-    <hyperlink ref="E233" r:id="rId229" xr:uid="{5DFB64BA-02DA-4E27-ABD1-F23E5ACE634C}"/>
-    <hyperlink ref="E234" r:id="rId230" xr:uid="{6538274C-3108-4180-BF59-7D2F60421961}"/>
-    <hyperlink ref="E235" r:id="rId231" xr:uid="{E3FF60F7-55EC-4CC9-B24E-0690C45B165B}"/>
-    <hyperlink ref="E236" r:id="rId232" xr:uid="{3AE184B2-BFE9-4008-B622-2E9EF517AA7E}"/>
-    <hyperlink ref="E237" r:id="rId233" xr:uid="{8C308EAB-0FA3-4A3A-AEB5-31028550EEE3}"/>
-    <hyperlink ref="E238" r:id="rId234" xr:uid="{9F3A4D46-1C2C-4605-AD06-3FDD23EADECD}"/>
-    <hyperlink ref="E239" r:id="rId235" xr:uid="{DF2C7296-3A80-48BD-9F4F-1B3FDE21D2A0}"/>
-    <hyperlink ref="E240" r:id="rId236" xr:uid="{35057412-EF2E-4985-A0E0-76A34E31DE37}"/>
-    <hyperlink ref="E241" r:id="rId237" xr:uid="{667DDF9D-9887-44D7-A1A4-9845701590C2}"/>
-    <hyperlink ref="E242" r:id="rId238" xr:uid="{FDE100D9-8470-4C9C-BE99-52A069D4A55E}"/>
-    <hyperlink ref="E243" r:id="rId239" xr:uid="{3DCA6EA8-7D98-4FF2-B349-F0464A02F6B0}"/>
-    <hyperlink ref="E244" r:id="rId240" xr:uid="{87219FCA-49A7-4D27-85F9-3CCC24E7E768}"/>
-    <hyperlink ref="E245" r:id="rId241" xr:uid="{E6371CBD-1A88-4664-BDF1-9EAEBB8DED6A}"/>
-    <hyperlink ref="E246" r:id="rId242" xr:uid="{E9C83AE0-4FE6-4CBB-87A0-E05B03AD6CC7}"/>
-    <hyperlink ref="E247" r:id="rId243" xr:uid="{8E506D21-1AED-4D69-B9AE-BB088B8A8276}"/>
-    <hyperlink ref="E248" r:id="rId244" xr:uid="{66EAE81F-C005-4780-BB92-714E34124E19}"/>
-    <hyperlink ref="E249" r:id="rId245" xr:uid="{A7285487-B267-488E-AEC7-FF520E347A8A}"/>
-    <hyperlink ref="E250" r:id="rId246" xr:uid="{75BF89C8-4097-4802-9A7C-1A4A9AC1D5E5}"/>
-    <hyperlink ref="E251" r:id="rId247" xr:uid="{69EFE573-D48A-44FE-A14A-4F07F4EB2109}"/>
+    <hyperlink ref="E86" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="E87" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="E88" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="E89" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="E90" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="E91" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="E92" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="E93" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="E94" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="E95" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="E96" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="E97" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="E98" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="E99" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="E100" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="E101" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="E102" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="E103" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="E104" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="E107" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="E108" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="E109" r:id="rId105" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="E110" r:id="rId106" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="E111" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="E112" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="E113" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="E114" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="E115" r:id="rId111" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="E116" r:id="rId112" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="E117" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="E118" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="E119" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="E120" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="E121" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
+    <hyperlink ref="E122" r:id="rId118" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
+    <hyperlink ref="E123" r:id="rId119" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
+    <hyperlink ref="E124" r:id="rId120" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="E126" r:id="rId121" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="E128" r:id="rId122" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="E129" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="E130" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="E131" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="E134" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="E135" r:id="rId127" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="E136" r:id="rId128" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="E137" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="E138" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="E139" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="E140" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="E141" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="E142" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="E143" r:id="rId135" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="E145" r:id="rId136" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="E146" r:id="rId137" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="E147" r:id="rId138" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="E148" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="E149" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="E150" r:id="rId141" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="E151" r:id="rId142" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="E155" r:id="rId143" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="E156" r:id="rId144" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="E157" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="E158" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="E159" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="E160" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="E161" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="E162" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="E163" r:id="rId151" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="E164" r:id="rId152" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="E165" r:id="rId153" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="E166" r:id="rId154" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="E167" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="E168" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="E169" r:id="rId157" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="E170" r:id="rId158" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="E171" r:id="rId159" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="E172" r:id="rId160" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="E173" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="E174" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="E175" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="E176" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="E177" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="E178" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="E179" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="E180" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="E181" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="E182" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="E183" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="E184" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="E185" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="E186" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="E187" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="E188" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="E189" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="E190" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="E192" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="E193" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="E194" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="E195" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="E197" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="E198" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="E199" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="E200" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="E201" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="E202" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="E203" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="E204" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="E205" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="E206" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="E207" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="E208" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="E209" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="E210" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="E211" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="E212" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="E213" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="E214" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="E215" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="E216" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="E217" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="E218" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="E220" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="E221" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="E222" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="E223" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="E224" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="E225" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="E226" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="E227" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="E228" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="E229" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="E230" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="E231" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="E232" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="E233" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="E234" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="E235" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="E236" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="E237" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="E238" r:id="rId223" xr:uid="{904B8D17-C758-4971-8887-D4B35A29A121}"/>
+    <hyperlink ref="E239" r:id="rId224" xr:uid="{C55E4301-F266-4FF0-90D1-66AA97D94E0B}"/>
+    <hyperlink ref="E240" r:id="rId225" xr:uid="{D32D4BE9-CE2E-4ACC-B97D-3203F7AAC7EC}"/>
+    <hyperlink ref="E241" r:id="rId226" xr:uid="{9B94C22A-3D34-48B2-8A45-20C2A23AD024}"/>
+    <hyperlink ref="E242" r:id="rId227" xr:uid="{8081B498-1E76-4942-B347-BF56C637B625}"/>
+    <hyperlink ref="E243" r:id="rId228" xr:uid="{F46741B3-19A7-4544-B08D-27F965CD11BF}"/>
+    <hyperlink ref="E244" r:id="rId229" xr:uid="{B27688E8-8D6F-4727-9C65-71DBF2928133}"/>
+    <hyperlink ref="E245" r:id="rId230" xr:uid="{0A05267F-CEFA-4AF9-A9F6-D35C1785BA08}"/>
+    <hyperlink ref="E246" r:id="rId231" xr:uid="{F92CF8AB-84A5-4DB1-9047-59C4C381B5A1}"/>
+    <hyperlink ref="E247" r:id="rId232" xr:uid="{16DC4AD3-D452-4363-9D84-7A207845EDE1}"/>
+    <hyperlink ref="E248" r:id="rId233" xr:uid="{2BBC1E3F-48FC-481C-81BE-2DB70840B2A3}"/>
+    <hyperlink ref="E249" r:id="rId234" xr:uid="{AC7AD88D-6ECD-44F9-A3FD-6ECA92BCAF4D}"/>
+    <hyperlink ref="E250" r:id="rId235" xr:uid="{4F0E68B5-2F50-47A5-9ED9-87DABC7CA0E4}"/>
+    <hyperlink ref="E251" r:id="rId236" xr:uid="{E1EFDCD6-8489-4336-800A-E694C7A9FE80}"/>
+    <hyperlink ref="E252" r:id="rId237" xr:uid="{3A804D64-BFCB-4005-95F8-7F1D3FF3DFA7}"/>
+    <hyperlink ref="E253" r:id="rId238" xr:uid="{BD4AFD11-9155-4174-95AB-3E851077E9FF}"/>
+    <hyperlink ref="E254" r:id="rId239" xr:uid="{E0109740-42D6-425C-9623-E6B5194837C9}"/>
+    <hyperlink ref="E255" r:id="rId240" xr:uid="{0992A860-178D-4E1D-8310-169AB2170121}"/>
+    <hyperlink ref="E256" r:id="rId241" xr:uid="{FAEEC584-0088-4781-A863-5C5BAC4F3633}"/>
+    <hyperlink ref="E257" r:id="rId242" xr:uid="{C391C98F-A9A3-4149-A7D2-E68C8DFC4A35}"/>
+    <hyperlink ref="E258" r:id="rId243" xr:uid="{042D1164-4203-4E49-BBFB-6CD5DD12BA55}"/>
+    <hyperlink ref="E259" r:id="rId244" xr:uid="{E5DE4B11-2DDB-4885-987A-66CCC49298F2}"/>
+    <hyperlink ref="E260" r:id="rId245" xr:uid="{A9243D4B-808A-40C0-84F0-57D1DCD2EE44}"/>
+    <hyperlink ref="E261" r:id="rId246" xr:uid="{54CF44C6-587D-43CE-8F56-09E054BE4BAF}"/>
+    <hyperlink ref="E262" r:id="rId247" xr:uid="{FEA0FA66-39A6-4A4F-B052-B713A5B0B412}"/>
+    <hyperlink ref="E263" r:id="rId248" xr:uid="{513F8969-3C3A-4258-845A-26E25FB3B753}"/>
+    <hyperlink ref="E264" r:id="rId249" xr:uid="{F0DC9703-D343-4E38-8537-AF235A5CCA1D}"/>
+    <hyperlink ref="E265" r:id="rId250" xr:uid="{EE534022-1A0F-44C0-A6E0-70A8DF334A4E}"/>
+    <hyperlink ref="E266" r:id="rId251" xr:uid="{A2723AF8-63E3-4BA1-8979-4803C6316177}"/>
+    <hyperlink ref="E267" r:id="rId252" xr:uid="{BA2D1B91-2D5F-491B-8C59-6976880F3B37}"/>
+    <hyperlink ref="E268" r:id="rId253" xr:uid="{61F39757-A048-4B2A-9B41-1A916F2096D4}"/>
+    <hyperlink ref="E269" r:id="rId254" xr:uid="{BED9478E-2742-443B-A9FA-06B87498F42E}"/>
+    <hyperlink ref="E270" r:id="rId255" xr:uid="{E2292BCD-D6D9-4143-B751-E17016800ED3}"/>
+    <hyperlink ref="E271" r:id="rId256" xr:uid="{66727670-7709-4BDA-AF3D-65FA6CCFAB7D}"/>
+    <hyperlink ref="E272" r:id="rId257" xr:uid="{6658022B-2C92-4908-9AEF-E163E61A979D}"/>
+    <hyperlink ref="E273" r:id="rId258" xr:uid="{6FBA0F26-D8C9-4279-B626-F600DDB4F17C}"/>
+    <hyperlink ref="E274" r:id="rId259" xr:uid="{70148CF5-8627-4337-99BE-72A419E30EFB}"/>
+    <hyperlink ref="E275" r:id="rId260" xr:uid="{5F69C956-2DA1-45B3-A4E7-0A7CEEF98F40}"/>
+    <hyperlink ref="E276" r:id="rId261" xr:uid="{6147BD96-E4EE-4C9C-9C34-E1523AAC48AB}"/>
+    <hyperlink ref="E277" r:id="rId262" xr:uid="{A3BFDE46-4FD3-4FB2-A188-46A1778D7879}"/>
+    <hyperlink ref="E278" r:id="rId263" xr:uid="{7E5C83DD-2D63-4958-A31A-435D3D2B1C00}"/>
+    <hyperlink ref="E279" r:id="rId264" xr:uid="{B88F2CBA-BBD8-49CE-90B7-DEA50B8DB554}"/>
+    <hyperlink ref="E280" r:id="rId265" xr:uid="{595456FF-5CCE-453A-8526-3A3202BDADF1}"/>
+    <hyperlink ref="E281" r:id="rId266" xr:uid="{5FA37B56-DDFA-4C6D-A95A-5B4841F02A6D}"/>
+    <hyperlink ref="E282" r:id="rId267" xr:uid="{19CC2746-3354-44C9-9C4C-BE47FE1EE527}"/>
+    <hyperlink ref="E283" r:id="rId268" xr:uid="{D71B5CEB-3134-4F18-BFF3-D3F9C38FF7E7}"/>
+    <hyperlink ref="E284" r:id="rId269" xr:uid="{7B7280D7-1F9E-4E4D-BB15-2BF81AC4D159}"/>
+    <hyperlink ref="E285" r:id="rId270" xr:uid="{02D5F013-2D77-42CD-8494-55C0C3ED79E3}"/>
+    <hyperlink ref="E286" r:id="rId271" xr:uid="{123F5578-7AB7-4994-B96C-46A9D6556E36}"/>
+    <hyperlink ref="E287" r:id="rId272" xr:uid="{F556BA12-83B8-42B8-AFDC-0D8C41FC301D}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
